--- a/player_stats/_stats_overall.xlsx
+++ b/player_stats/_stats_overall.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="DieseArbeitsmappe"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="7" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="7" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-13" sheetId="1" state="visible" r:id="rId1"/>
@@ -328,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -497,28 +497,28 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
@@ -534,8 +534,8 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="1" hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -548,14 +548,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -566,21 +558,27 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -958,13 +956,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:CL64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.5546875" bestFit="1" customWidth="1" style="103" min="1" max="1"/>
+    <col width="18.5703125" bestFit="1" customWidth="1" style="91" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.4" customHeight="1" s="103">
-      <c r="E1" s="91" t="inlineStr">
+    <row r="1" ht="35.45" customHeight="1" s="91">
+      <c r="E1" s="90" t="inlineStr">
         <is>
           <t>Saison 12/13</t>
         </is>
@@ -1343,7 +1341,7 @@
       <c r="CH3" s="42" t="n"/>
       <c r="CI3" s="42" t="n"/>
     </row>
-    <row r="4" ht="241.8" customHeight="1" s="103">
+    <row r="4" ht="241.9" customHeight="1" s="91">
       <c r="A4" s="94" t="n"/>
       <c r="B4" s="94" t="n"/>
       <c r="C4" s="97" t="n"/>
@@ -6667,17 +6665,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1"/>
+  <dimension ref="A1:R65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col width="20.33203125" customWidth="1" style="103" min="1" max="1"/>
-    <col width="15.44140625" customWidth="1" style="103" min="2" max="2"/>
-    <col width="13.5546875" customWidth="1" style="103" min="3" max="4"/>
-    <col width="13.33203125" customWidth="1" style="103" min="5" max="6"/>
-    <col width="12.5546875" customWidth="1" style="103" min="7" max="8"/>
+    <col width="20.28515625" customWidth="1" style="91" min="1" max="1"/>
+    <col width="15.42578125" customWidth="1" style="91" min="2" max="2"/>
+    <col width="13.5703125" customWidth="1" style="91" min="3" max="4"/>
+    <col width="13.28515625" customWidth="1" style="91" min="5" max="6"/>
+    <col width="12.5703125" customWidth="1" style="91" min="7" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.4" customHeight="1" s="103">
+    <row r="1" ht="23.45" customHeight="1" s="91">
       <c r="A1" s="36" t="n"/>
       <c r="B1" s="88" t="inlineStr">
         <is>
@@ -6701,7 +6699,7 @@
       <c r="Q1" s="38" t="n"/>
       <c r="R1" s="38" t="n"/>
     </row>
-    <row r="2" ht="23.4" customHeight="1" s="103">
+    <row r="2" ht="23.45" customHeight="1" s="91">
       <c r="A2" s="36" t="n"/>
       <c r="B2" s="34" t="n"/>
       <c r="C2" s="34" t="n"/>
@@ -6721,7 +6719,7 @@
       <c r="Q2" s="38" t="n"/>
       <c r="R2" s="38" t="n"/>
     </row>
-    <row r="3" ht="23.4" customHeight="1" s="103">
+    <row r="3" ht="23.45" customHeight="1" s="91">
       <c r="A3" s="35" t="n"/>
       <c r="B3" s="86" t="inlineStr">
         <is>
@@ -6767,7 +6765,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1" s="103">
+    <row r="4" ht="22.5" customHeight="1" s="91">
       <c r="A4" s="35" t="n"/>
       <c r="B4" s="86" t="inlineStr">
         <is>
@@ -6786,43 +6784,43 @@
         </is>
       </c>
       <c r="J4" s="38">
-        <f>COUNTIF($I$8:$I$57,"150")</f>
+        <f>COUNTIF($I$8:$I$58,"150")</f>
         <v/>
       </c>
       <c r="K4" s="38">
-        <f>COUNTIF($I$8:$I$57,"200")</f>
+        <f>COUNTIF($I$8:$I$58,"200")</f>
         <v/>
       </c>
       <c r="L4" s="38">
-        <f>COUNTIF($I$8:$I$57,"250")</f>
+        <f>COUNTIF($I$8:$I$58,"250")</f>
         <v/>
       </c>
       <c r="M4" s="38">
-        <f>COUNTIF($I$8:$I$57,"300")</f>
+        <f>COUNTIF($I$8:$I$58,"300")</f>
         <v/>
       </c>
       <c r="N4" s="38">
-        <f>COUNTIF($I$8:$I$57,"350")</f>
+        <f>COUNTIF($I$8:$I$58,"350")</f>
         <v/>
       </c>
       <c r="O4" s="38">
-        <f>COUNTIF($I$8:$I$57,"400")</f>
+        <f>COUNTIF($I$8:$I$58,"400")</f>
         <v/>
       </c>
       <c r="P4" s="38">
-        <f>COUNTIF($I$8:$I$57,"450")</f>
+        <f>COUNTIF($I$8:$I$58,"450")</f>
         <v/>
       </c>
       <c r="Q4" s="38">
-        <f>COUNTIF($I$8:$I$57,"500")</f>
+        <f>COUNTIF($I$8:$I$58,"500")</f>
         <v/>
       </c>
       <c r="R4" s="38">
-        <f>COUNTIF($I$8:$I$57,"550")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1" s="103">
+        <f>COUNTIF($I$8:$I$58,"550")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1" s="91">
       <c r="A5" s="35" t="n"/>
       <c r="B5" s="86" t="n"/>
       <c r="C5" s="86" t="n"/>
@@ -6842,7 +6840,7 @@
       <c r="Q5" s="38" t="n"/>
       <c r="R5" s="38" t="n"/>
     </row>
-    <row r="6" ht="23.4" customHeight="1" s="103">
+    <row r="6" ht="23.45" customHeight="1" s="91">
       <c r="A6" s="36" t="n"/>
       <c r="B6" s="89" t="inlineStr">
         <is>
@@ -6872,7 +6870,7 @@
       <c r="Q6" s="38" t="n"/>
       <c r="R6" s="38" t="n"/>
     </row>
-    <row r="7" ht="13.95" customHeight="1" s="103">
+    <row r="7" ht="13.9" customHeight="1" s="91">
       <c r="A7" s="35" t="n"/>
       <c r="B7" s="87" t="n"/>
       <c r="C7" s="31" t="inlineStr">
@@ -6916,2333 +6914,2353 @@
       <c r="Q7" s="38" t="n"/>
       <c r="R7" s="38" t="n"/>
     </row>
-    <row r="8" ht="13.2" customHeight="1" s="103">
-      <c r="A8" s="104" t="inlineStr">
+    <row r="8" ht="13.15" customHeight="1" s="91">
+      <c r="A8" s="100" t="inlineStr">
         <is>
           <t>Auber, Daniel</t>
         </is>
       </c>
-      <c r="B8" s="105">
+      <c r="B8" s="101">
         <f>'24-25'!H8</f>
         <v/>
       </c>
-      <c r="C8" s="105" t="n">
+      <c r="C8" s="101" t="n">
         <v>14</v>
       </c>
-      <c r="D8" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="105" t="n">
+      <c r="D8" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="105" t="n"/>
-      <c r="G8" s="105">
-        <f>SUM(C8:F8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="105">
-        <f>B8+G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="106">
+      <c r="F8" s="101" t="n"/>
+      <c r="G8" s="101">
+        <f>C8+D8+E8+F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="101">
+        <f>G8+B8</f>
+        <v/>
+      </c>
+      <c r="I8" s="113">
         <f>IFERROR(LOOKUP(2,1/((B8&lt;$J$3:$R$3)*(H8&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J8" s="105" t="n"/>
-      <c r="K8" s="105" t="n"/>
-      <c r="L8" s="105" t="n"/>
-      <c r="M8" s="105" t="n"/>
-      <c r="N8" s="105" t="n"/>
-      <c r="O8" s="105" t="n"/>
-      <c r="P8" s="105" t="n"/>
-      <c r="Q8" s="105" t="n"/>
-      <c r="R8" s="105" t="n"/>
-    </row>
-    <row r="9" ht="13.2" customHeight="1" s="103">
-      <c r="A9" s="107" t="inlineStr">
+      <c r="J8" s="101" t="n"/>
+      <c r="K8" s="101" t="n"/>
+      <c r="L8" s="101" t="n"/>
+      <c r="M8" s="101" t="n"/>
+      <c r="N8" s="101" t="n"/>
+      <c r="O8" s="101" t="n"/>
+      <c r="P8" s="101" t="n"/>
+      <c r="Q8" s="101" t="n"/>
+      <c r="R8" s="101" t="n"/>
+    </row>
+    <row r="9" ht="13.15" customHeight="1" s="91">
+      <c r="A9" s="103" t="inlineStr">
         <is>
           <t>Auber, David</t>
         </is>
       </c>
-      <c r="B9" s="108">
+      <c r="B9" s="104">
         <f>'24-25'!H9</f>
         <v/>
       </c>
-      <c r="C9" s="108" t="n">
+      <c r="C9" s="104" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="108" t="n">
+      <c r="D9" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="104" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="108" t="n"/>
-      <c r="G9" s="108">
-        <f>SUM(C9:F9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="108">
-        <f>B9+G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="109">
+      <c r="F9" s="104" t="n"/>
+      <c r="G9" s="104">
+        <f>C9+D9+E9+F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="104">
+        <f>G9+B9</f>
+        <v/>
+      </c>
+      <c r="I9" s="114">
         <f>IFERROR(LOOKUP(2,1/((B9&lt;$J$3:$R$3)*(H9&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J9" s="108" t="n"/>
-      <c r="K9" s="108" t="n"/>
-      <c r="L9" s="108" t="n"/>
-      <c r="M9" s="108" t="n"/>
-      <c r="N9" s="108" t="n"/>
-      <c r="O9" s="108" t="n"/>
-      <c r="P9" s="108" t="n"/>
-      <c r="Q9" s="108" t="n"/>
-      <c r="R9" s="108" t="n"/>
-    </row>
-    <row r="10" ht="13.2" customHeight="1" s="103">
-      <c r="A10" s="104" t="inlineStr">
+      <c r="J9" s="104" t="n"/>
+      <c r="K9" s="104" t="n"/>
+      <c r="L9" s="104" t="n"/>
+      <c r="M9" s="104" t="n"/>
+      <c r="N9" s="104" t="n"/>
+      <c r="O9" s="104" t="n"/>
+      <c r="P9" s="104" t="n"/>
+      <c r="Q9" s="104" t="n"/>
+      <c r="R9" s="104" t="n"/>
+    </row>
+    <row r="10" ht="13.15" customHeight="1" s="91">
+      <c r="A10" s="100" t="inlineStr">
         <is>
           <t>Auber, Manuel</t>
         </is>
       </c>
-      <c r="B10" s="105">
+      <c r="B10" s="101">
         <f>'24-25'!H10</f>
         <v/>
       </c>
-      <c r="C10" s="105" t="n">
+      <c r="C10" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="105" t="n">
+      <c r="D10" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="101" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="105" t="n"/>
-      <c r="G10" s="105">
-        <f>SUM(C10:F10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="105">
-        <f>B10+G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="106">
+      <c r="F10" s="101" t="n"/>
+      <c r="G10" s="101">
+        <f>C10+D10+E10+F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="101">
+        <f>G10+B10</f>
+        <v/>
+      </c>
+      <c r="I10" s="113">
         <f>IFERROR(LOOKUP(2,1/((B10&lt;$J$3:$R$3)*(H10&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J10" s="105" t="n"/>
-      <c r="K10" s="105" t="n"/>
-      <c r="L10" s="105" t="n"/>
-      <c r="M10" s="105" t="n"/>
-      <c r="N10" s="105" t="n"/>
-      <c r="O10" s="105" t="n"/>
-      <c r="P10" s="105" t="n"/>
-      <c r="Q10" s="105" t="n"/>
-      <c r="R10" s="105" t="n"/>
-    </row>
-    <row r="11" ht="13.2" customHeight="1" s="103">
-      <c r="A11" s="107" t="inlineStr">
+      <c r="J10" s="101" t="n"/>
+      <c r="K10" s="101" t="n"/>
+      <c r="L10" s="101" t="n"/>
+      <c r="M10" s="101" t="n"/>
+      <c r="N10" s="101" t="n"/>
+      <c r="O10" s="101" t="n"/>
+      <c r="P10" s="101" t="n"/>
+      <c r="Q10" s="101" t="n"/>
+      <c r="R10" s="101" t="n"/>
+    </row>
+    <row r="11" ht="13.15" customHeight="1" s="91">
+      <c r="A11" s="103" t="inlineStr">
         <is>
           <t>Auber, Matthias</t>
         </is>
       </c>
-      <c r="B11" s="110">
+      <c r="B11" s="104">
+        <f>'24-25'!H11</f>
+        <v/>
+      </c>
+      <c r="C11" s="104" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="104" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="104" t="n"/>
+      <c r="G11" s="104">
+        <f>C11+D11+E11+F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="104">
+        <f>G11+B11</f>
+        <v/>
+      </c>
+      <c r="I11" s="114">
+        <f>IFERROR(LOOKUP(2,1/((B11&lt;$J$3:$R$3)*(H11&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="104" t="n"/>
+      <c r="K11" s="104" t="n"/>
+      <c r="L11" s="104" t="n"/>
+      <c r="M11" s="104" t="n"/>
+      <c r="N11" s="104" t="n"/>
+      <c r="O11" s="104" t="n"/>
+      <c r="P11" s="104" t="n"/>
+      <c r="Q11" s="104" t="n"/>
+      <c r="R11" s="104" t="n"/>
+    </row>
+    <row r="12" ht="13.15" customHeight="1" s="91">
+      <c r="A12" s="100" t="inlineStr">
+        <is>
+          <t>Beck, Ronny</t>
+        </is>
+      </c>
+      <c r="B12" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C11" s="108" t="n">
+      <c r="C12" s="101" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="101" t="n"/>
+      <c r="G12" s="101">
+        <f>C12+D12+E12+F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="101">
+        <f>G12+B12</f>
+        <v/>
+      </c>
+      <c r="I12" s="113">
+        <f>IFERROR(LOOKUP(2,1/((B12&lt;$J$3:$R$3)*(H12&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="101" t="n"/>
+      <c r="K12" s="101" t="n"/>
+      <c r="L12" s="101" t="n"/>
+      <c r="M12" s="101" t="n"/>
+      <c r="N12" s="101" t="n"/>
+      <c r="O12" s="101" t="n"/>
+      <c r="P12" s="101" t="n"/>
+      <c r="Q12" s="101" t="n"/>
+      <c r="R12" s="101" t="n"/>
+    </row>
+    <row r="13" ht="13.15" customHeight="1" s="91">
+      <c r="A13" s="103" t="inlineStr">
+        <is>
+          <t>Benner, Florian</t>
+        </is>
+      </c>
+      <c r="B13" s="104">
+        <f>'24-25'!H14</f>
+        <v/>
+      </c>
+      <c r="C13" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="104" t="n"/>
+      <c r="G13" s="104">
+        <f>C13+D13+E13+F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="104">
+        <f>G13+B13</f>
+        <v/>
+      </c>
+      <c r="I13" s="114">
+        <f>IFERROR(LOOKUP(2,1/((B13&lt;$J$3:$R$3)*(H13&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="104" t="n"/>
+      <c r="K13" s="104" t="n"/>
+      <c r="L13" s="104" t="n"/>
+      <c r="M13" s="104" t="n"/>
+      <c r="N13" s="104" t="n"/>
+      <c r="O13" s="104" t="n"/>
+      <c r="P13" s="104" t="n"/>
+      <c r="Q13" s="104" t="n"/>
+      <c r="R13" s="104" t="n"/>
+    </row>
+    <row r="14" ht="13.15" customHeight="1" s="91">
+      <c r="A14" s="100" t="inlineStr">
+        <is>
+          <t>Berger, Ruben</t>
+        </is>
+      </c>
+      <c r="B14" s="106">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C14" s="101" t="n">
+        <v>17</v>
+      </c>
+      <c r="D14" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="101" t="n"/>
+      <c r="G14" s="101">
+        <f>C14+D14+E14+F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="101">
+        <f>G14+B14</f>
+        <v/>
+      </c>
+      <c r="I14" s="113">
+        <f>IFERROR(LOOKUP(2,1/((B14&lt;$J$3:$R$3)*(H14&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="101" t="n"/>
+      <c r="K14" s="101" t="n"/>
+      <c r="L14" s="101" t="n"/>
+      <c r="M14" s="101" t="n"/>
+      <c r="N14" s="101" t="n"/>
+      <c r="O14" s="101" t="n"/>
+      <c r="P14" s="101" t="n"/>
+      <c r="Q14" s="101" t="n"/>
+      <c r="R14" s="101" t="n"/>
+    </row>
+    <row r="15" ht="13.15" customHeight="1" s="91">
+      <c r="A15" s="103" t="inlineStr">
+        <is>
+          <t>Bister, Manuel</t>
+        </is>
+      </c>
+      <c r="B15" s="107">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C15" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="104" t="n"/>
+      <c r="G15" s="104">
+        <f>C15+D15+E15+F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="104">
+        <f>G15+B15</f>
+        <v/>
+      </c>
+      <c r="I15" s="114">
+        <f>IFERROR(LOOKUP(2,1/((B15&lt;$J$3:$R$3)*(H15&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="104" t="n"/>
+      <c r="K15" s="104" t="n"/>
+      <c r="L15" s="104" t="n"/>
+      <c r="M15" s="104" t="n"/>
+      <c r="N15" s="104" t="n"/>
+      <c r="O15" s="104" t="n"/>
+      <c r="P15" s="104" t="n"/>
+      <c r="Q15" s="104" t="n"/>
+      <c r="R15" s="104" t="n"/>
+    </row>
+    <row r="16" ht="13.15" customHeight="1" s="91">
+      <c r="A16" s="100" t="inlineStr">
+        <is>
+          <t>Blechschmidt, Marvin</t>
+        </is>
+      </c>
+      <c r="B16" s="106">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C16" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="101" t="n"/>
+      <c r="G16" s="101">
+        <f>C16+D16+E16+F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="101">
+        <f>G16+B16</f>
+        <v/>
+      </c>
+      <c r="I16" s="113">
+        <f>IFERROR(LOOKUP(2,1/((B16&lt;$J$3:$R$3)*(H16&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="101" t="n"/>
+      <c r="K16" s="101" t="n"/>
+      <c r="L16" s="101" t="n"/>
+      <c r="M16" s="101" t="n"/>
+      <c r="N16" s="101" t="n"/>
+      <c r="O16" s="101" t="n"/>
+      <c r="P16" s="101" t="n"/>
+      <c r="Q16" s="101" t="n"/>
+      <c r="R16" s="101" t="n"/>
+    </row>
+    <row r="17" ht="13.15" customHeight="1" s="91">
+      <c r="A17" s="103" t="inlineStr">
+        <is>
+          <t>Bühner, Ahmad Reza</t>
+        </is>
+      </c>
+      <c r="B17" s="104">
+        <f>'24-25'!H17</f>
+        <v/>
+      </c>
+      <c r="C17" s="104" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="104" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="104" t="n"/>
+      <c r="G17" s="104">
+        <f>C17+D17+E17+F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="104">
+        <f>G17+B17</f>
+        <v/>
+      </c>
+      <c r="I17" s="114">
+        <f>IFERROR(LOOKUP(2,1/((B17&lt;$J$3:$R$3)*(H17&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="104" t="n"/>
+      <c r="K17" s="104" t="n"/>
+      <c r="L17" s="104" t="n"/>
+      <c r="M17" s="104" t="n"/>
+      <c r="N17" s="104" t="n"/>
+      <c r="O17" s="104" t="n"/>
+      <c r="P17" s="104" t="n"/>
+      <c r="Q17" s="104" t="n"/>
+      <c r="R17" s="104" t="n"/>
+    </row>
+    <row r="18" ht="13.15" customHeight="1" s="91">
+      <c r="A18" s="100" t="inlineStr">
+        <is>
+          <t>Dold, Markus</t>
+        </is>
+      </c>
+      <c r="B18" s="101">
+        <f>'24-25'!H19</f>
+        <v/>
+      </c>
+      <c r="C18" s="101" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="101" t="n"/>
+      <c r="G18" s="101">
+        <f>C18+D18+E18+F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="101">
+        <f>G18+B18</f>
+        <v/>
+      </c>
+      <c r="I18" s="113">
+        <f>IFERROR(LOOKUP(2,1/((B18&lt;$J$3:$R$3)*(H18&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="101" t="n"/>
+      <c r="K18" s="101" t="n"/>
+      <c r="L18" s="101" t="n"/>
+      <c r="M18" s="101" t="n"/>
+      <c r="N18" s="101" t="n"/>
+      <c r="O18" s="101" t="n"/>
+      <c r="P18" s="101" t="n"/>
+      <c r="Q18" s="101" t="n"/>
+      <c r="R18" s="101" t="n"/>
+    </row>
+    <row r="19" ht="13.15" customHeight="1" s="91">
+      <c r="A19" s="103" t="inlineStr">
+        <is>
+          <t>Flaig, Elias</t>
+        </is>
+      </c>
+      <c r="B19" s="104">
+        <f>'24-25'!H21</f>
+        <v/>
+      </c>
+      <c r="C19" s="104" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="108" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" s="108" t="n"/>
-      <c r="G11" s="108">
-        <f>SUM(C11:F11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="108">
-        <f>B11+G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="109">
-        <f>IFERROR(LOOKUP(2,1/((B11&lt;$J$3:$R$3)*(H11&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="108" t="n"/>
-      <c r="K11" s="108" t="n"/>
-      <c r="L11" s="108" t="n"/>
-      <c r="M11" s="108" t="n"/>
-      <c r="N11" s="108" t="n"/>
-      <c r="O11" s="108" t="n"/>
-      <c r="P11" s="108" t="n"/>
-      <c r="Q11" s="108" t="n"/>
-      <c r="R11" s="108" t="n"/>
-    </row>
-    <row r="12" ht="13.2" customHeight="1" s="103">
-      <c r="A12" s="104" t="inlineStr">
-        <is>
-          <t>Beck, Ronny</t>
-        </is>
-      </c>
-      <c r="B12" s="111">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C12" s="105" t="n">
-        <v>16</v>
-      </c>
-      <c r="D12" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="105" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="105" t="n"/>
-      <c r="G12" s="105">
-        <f>SUM(C12:F12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="105">
-        <f>B12+G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="106">
-        <f>IFERROR(LOOKUP(2,1/((B12&lt;$J$3:$R$3)*(H12&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="105" t="n"/>
-      <c r="K12" s="105" t="n"/>
-      <c r="L12" s="105" t="n"/>
-      <c r="M12" s="105" t="n"/>
-      <c r="N12" s="105" t="n"/>
-      <c r="O12" s="105" t="n"/>
-      <c r="P12" s="105" t="n"/>
-      <c r="Q12" s="105" t="n"/>
-      <c r="R12" s="105" t="n"/>
-    </row>
-    <row r="13" ht="13.2" customHeight="1" s="103">
-      <c r="A13" s="107" t="inlineStr">
-        <is>
-          <t>Benner, Florian</t>
-        </is>
-      </c>
-      <c r="B13" s="108">
-        <f>'24-25'!H14</f>
-        <v/>
-      </c>
-      <c r="C13" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="108" t="n"/>
-      <c r="G13" s="108">
-        <f>SUM(C13:F13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="108">
-        <f>B13+G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="109">
-        <f>IFERROR(LOOKUP(2,1/((B13&lt;$J$3:$R$3)*(H13&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="108" t="n"/>
-      <c r="K13" s="108" t="n"/>
-      <c r="L13" s="108" t="n"/>
-      <c r="M13" s="108" t="n"/>
-      <c r="N13" s="108" t="n"/>
-      <c r="O13" s="108" t="n"/>
-      <c r="P13" s="108" t="n"/>
-      <c r="Q13" s="108" t="n"/>
-      <c r="R13" s="108" t="n"/>
-    </row>
-    <row r="14" ht="13.2" customHeight="1" s="103">
-      <c r="A14" s="104" t="inlineStr">
-        <is>
-          <t>Berger, Ruben</t>
-        </is>
-      </c>
-      <c r="B14" s="111">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C14" s="105" t="n">
-        <v>17</v>
-      </c>
-      <c r="D14" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="105" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="105" t="n"/>
-      <c r="G14" s="105">
-        <f>SUM(C14:F14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="105">
-        <f>B14+G14</f>
-        <v/>
-      </c>
-      <c r="I14" s="106">
-        <f>IFERROR(LOOKUP(2,1/((B14&lt;$J$3:$R$3)*(H14&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="105" t="n"/>
-      <c r="K14" s="105" t="n"/>
-      <c r="L14" s="105" t="n"/>
-      <c r="M14" s="105" t="n"/>
-      <c r="N14" s="105" t="n"/>
-      <c r="O14" s="105" t="n"/>
-      <c r="P14" s="105" t="n"/>
-      <c r="Q14" s="105" t="n"/>
-      <c r="R14" s="105" t="n"/>
-    </row>
-    <row r="15" ht="13.2" customHeight="1" s="103">
-      <c r="A15" s="107" t="inlineStr">
-        <is>
-          <t>Bister, Manuel</t>
-        </is>
-      </c>
-      <c r="B15" s="110">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C15" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="108" t="n"/>
-      <c r="G15" s="108">
-        <f>SUM(C15:F15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="108">
-        <f>B15+G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="109">
-        <f>IFERROR(LOOKUP(2,1/((B15&lt;$J$3:$R$3)*(H15&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="108" t="n"/>
-      <c r="K15" s="108" t="n"/>
-      <c r="L15" s="108" t="n"/>
-      <c r="M15" s="108" t="n"/>
-      <c r="N15" s="108" t="n"/>
-      <c r="O15" s="108" t="n"/>
-      <c r="P15" s="108" t="n"/>
-      <c r="Q15" s="108" t="n"/>
-      <c r="R15" s="108" t="n"/>
-    </row>
-    <row r="16" ht="13.2" customHeight="1" s="103">
-      <c r="A16" s="104" t="inlineStr">
-        <is>
-          <t>Blechschmidt, Marvin</t>
-        </is>
-      </c>
-      <c r="B16" s="111">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C16" s="105" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="105" t="n"/>
-      <c r="G16" s="105">
-        <f>SUM(C16:F16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="105">
-        <f>B16+G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="106">
-        <f>IFERROR(LOOKUP(2,1/((B16&lt;$J$3:$R$3)*(H16&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="105" t="n"/>
-      <c r="K16" s="105" t="n"/>
-      <c r="L16" s="105" t="n"/>
-      <c r="M16" s="105" t="n"/>
-      <c r="N16" s="105" t="n"/>
-      <c r="O16" s="105" t="n"/>
-      <c r="P16" s="105" t="n"/>
-      <c r="Q16" s="105" t="n"/>
-      <c r="R16" s="105" t="n"/>
-    </row>
-    <row r="17" ht="13.2" customHeight="1" s="103">
-      <c r="A17" s="107" t="inlineStr">
-        <is>
-          <t>Bühner, Ahmad Reza</t>
-        </is>
-      </c>
-      <c r="B17" s="110">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C17" s="108" t="n">
-        <v>15</v>
-      </c>
-      <c r="D17" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="108" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" s="108" t="n"/>
-      <c r="G17" s="108">
-        <f>SUM(C17:F17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="108">
-        <f>B17+G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="109">
-        <f>IFERROR(LOOKUP(2,1/((B17&lt;$J$3:$R$3)*(H17&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="108" t="n"/>
-      <c r="K17" s="108" t="n"/>
-      <c r="L17" s="108" t="n"/>
-      <c r="M17" s="108" t="n"/>
-      <c r="N17" s="108" t="n"/>
-      <c r="O17" s="108" t="n"/>
-      <c r="P17" s="108" t="n"/>
-      <c r="Q17" s="108" t="n"/>
-      <c r="R17" s="108" t="n"/>
-    </row>
-    <row r="18" ht="13.2" customHeight="1" s="103">
-      <c r="A18" s="104" t="inlineStr">
-        <is>
-          <t>Dold, Markus</t>
-        </is>
-      </c>
-      <c r="B18" s="105">
-        <f>'24-25'!H19</f>
-        <v/>
-      </c>
-      <c r="C18" s="105" t="n">
-        <v>20</v>
-      </c>
-      <c r="D18" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="105" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="105" t="n"/>
-      <c r="G18" s="105">
-        <f>SUM(C18:F18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="105">
-        <f>B18+G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="106">
-        <f>IFERROR(LOOKUP(2,1/((B18&lt;$J$3:$R$3)*(H18&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="105" t="n"/>
-      <c r="K18" s="105" t="n"/>
-      <c r="L18" s="105" t="n"/>
-      <c r="M18" s="105" t="n"/>
-      <c r="N18" s="105" t="n"/>
-      <c r="O18" s="105" t="n"/>
-      <c r="P18" s="105" t="n"/>
-      <c r="Q18" s="105" t="n"/>
-      <c r="R18" s="105" t="n"/>
-    </row>
-    <row r="19" ht="13.2" customHeight="1" s="103">
-      <c r="A19" s="107" t="inlineStr">
-        <is>
-          <t>Flaig, Elias</t>
-        </is>
-      </c>
-      <c r="B19" s="108">
-        <f>'24-25'!H21</f>
-        <v/>
-      </c>
-      <c r="C19" s="108" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="108" t="n">
+      <c r="D19" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="104" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="108" t="n"/>
-      <c r="G19" s="108">
-        <f>SUM(C19:F19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="108">
-        <f>B19+G19</f>
-        <v/>
-      </c>
-      <c r="I19" s="112">
+      <c r="F19" s="104" t="n"/>
+      <c r="G19" s="104">
+        <f>C19+D19+E19+F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="104">
+        <f>G19+B19</f>
+        <v/>
+      </c>
+      <c r="I19" s="114">
         <f>IFERROR(LOOKUP(2,1/((B19&lt;$J$3:$R$3)*(H19&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J19" s="108" t="n"/>
-      <c r="K19" s="108" t="n"/>
-      <c r="L19" s="108" t="n"/>
-      <c r="M19" s="108" t="n"/>
-      <c r="N19" s="108" t="n"/>
-      <c r="O19" s="108" t="n"/>
-      <c r="P19" s="108" t="n"/>
-      <c r="Q19" s="108" t="n"/>
-      <c r="R19" s="108" t="n"/>
-    </row>
-    <row r="20" ht="13.2" customHeight="1" s="103">
-      <c r="A20" s="104" t="inlineStr">
+      <c r="J19" s="104" t="n"/>
+      <c r="K19" s="104" t="n"/>
+      <c r="L19" s="104" t="n"/>
+      <c r="M19" s="104" t="n"/>
+      <c r="N19" s="104" t="n"/>
+      <c r="O19" s="104" t="n"/>
+      <c r="P19" s="104" t="n"/>
+      <c r="Q19" s="104" t="n"/>
+      <c r="R19" s="104" t="n"/>
+    </row>
+    <row r="20" ht="13.15" customHeight="1" s="91">
+      <c r="A20" s="100" t="inlineStr">
         <is>
           <t>Flaig, Luis</t>
         </is>
       </c>
-      <c r="B20" s="105">
+      <c r="B20" s="101">
         <f>'24-25'!H22</f>
         <v/>
       </c>
-      <c r="C20" s="105" t="n">
+      <c r="C20" s="101" t="n">
         <v>22</v>
       </c>
-      <c r="D20" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="105" t="n">
+      <c r="D20" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="101" t="n">
         <v>7</v>
       </c>
-      <c r="F20" s="105" t="n"/>
-      <c r="G20" s="105">
-        <f>SUM(C20:F20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="105">
-        <f>B20+G20</f>
+      <c r="F20" s="101" t="n"/>
+      <c r="G20" s="101">
+        <f>C20+D20+E20+F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="101">
+        <f>G20+B20</f>
         <v/>
       </c>
       <c r="I20" s="113">
         <f>IFERROR(LOOKUP(2,1/((B20&lt;$J$3:$R$3)*(H20&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J20" s="105" t="n"/>
-      <c r="K20" s="105" t="n"/>
-      <c r="L20" s="105" t="n"/>
-      <c r="M20" s="105" t="n"/>
-      <c r="N20" s="105" t="n"/>
-      <c r="O20" s="105" t="n"/>
-      <c r="P20" s="105" t="n"/>
-      <c r="Q20" s="105" t="n"/>
-      <c r="R20" s="105" t="n"/>
-    </row>
-    <row r="21" ht="13.2" customHeight="1" s="103">
-      <c r="A21" s="107" t="inlineStr">
+      <c r="J20" s="101" t="n"/>
+      <c r="K20" s="101" t="n"/>
+      <c r="L20" s="101" t="n"/>
+      <c r="M20" s="101" t="n"/>
+      <c r="N20" s="101" t="n"/>
+      <c r="O20" s="101" t="n"/>
+      <c r="P20" s="101" t="n"/>
+      <c r="Q20" s="101" t="n"/>
+      <c r="R20" s="101" t="n"/>
+    </row>
+    <row r="21" ht="13.15" customHeight="1" s="91">
+      <c r="A21" s="103" t="inlineStr">
         <is>
           <t>Flaig, Tim</t>
         </is>
       </c>
-      <c r="B21" s="108">
-        <f>'24-25'!H23</f>
-        <v/>
-      </c>
-      <c r="C21" s="108" t="n">
+      <c r="B21" s="104">
+        <f>'24-25'!H24</f>
+        <v/>
+      </c>
+      <c r="C21" s="104" t="n">
         <v>17</v>
       </c>
-      <c r="D21" s="108" t="n">
+      <c r="D21" s="104" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="108" t="n">
+      <c r="E21" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="F21" s="108" t="n"/>
-      <c r="G21" s="108">
-        <f>SUM(C21:F21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="108">
-        <f>B21+G21</f>
-        <v/>
-      </c>
-      <c r="I21" s="112">
+      <c r="F21" s="104" t="n"/>
+      <c r="G21" s="104">
+        <f>C21+D21+E21+F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="104">
+        <f>G21+B21</f>
+        <v/>
+      </c>
+      <c r="I21" s="114">
         <f>IFERROR(LOOKUP(2,1/((B21&lt;$J$3:$R$3)*(H21&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J21" s="108" t="n"/>
-      <c r="K21" s="108" t="n"/>
-      <c r="L21" s="108" t="n"/>
-      <c r="M21" s="108" t="n"/>
-      <c r="N21" s="108" t="n"/>
-      <c r="O21" s="108" t="n"/>
-      <c r="P21" s="108" t="n"/>
-      <c r="Q21" s="108" t="n"/>
-      <c r="R21" s="108" t="n"/>
-    </row>
-    <row r="22" ht="13.2" customHeight="1" s="103">
-      <c r="A22" s="104" t="inlineStr">
+      <c r="J21" s="104" t="n"/>
+      <c r="K21" s="104" t="n"/>
+      <c r="L21" s="104" t="n"/>
+      <c r="M21" s="104" t="n"/>
+      <c r="N21" s="104" t="n"/>
+      <c r="O21" s="104" t="n"/>
+      <c r="P21" s="104" t="n"/>
+      <c r="Q21" s="104" t="n"/>
+      <c r="R21" s="104" t="n"/>
+    </row>
+    <row r="22" ht="13.15" customHeight="1" s="91">
+      <c r="A22" s="100" t="inlineStr">
         <is>
           <t>Fleig, Maximilian</t>
         </is>
       </c>
-      <c r="B22" s="105">
-        <f>'24-25'!H24</f>
-        <v/>
-      </c>
-      <c r="C22" s="105" t="n">
+      <c r="B22" s="101">
+        <f>'24-25'!H25</f>
+        <v/>
+      </c>
+      <c r="C22" s="101" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="105" t="n">
+      <c r="D22" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="101" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="105" t="n"/>
-      <c r="G22" s="105">
-        <f>SUM(C22:F22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="105">
-        <f>B22+G22</f>
+      <c r="F22" s="101" t="n"/>
+      <c r="G22" s="101">
+        <f>C22+D22+E22+F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="101">
+        <f>G22+B22</f>
         <v/>
       </c>
       <c r="I22" s="113">
         <f>IFERROR(LOOKUP(2,1/((B22&lt;$J$3:$R$3)*(H22&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J22" s="105" t="n"/>
-      <c r="K22" s="105" t="n"/>
-      <c r="L22" s="105" t="n"/>
-      <c r="M22" s="105" t="n"/>
-      <c r="N22" s="105" t="n"/>
-      <c r="O22" s="105" t="n"/>
-      <c r="P22" s="105" t="n"/>
-      <c r="Q22" s="105" t="n"/>
-      <c r="R22" s="105" t="n"/>
-    </row>
-    <row r="23" ht="13.2" customHeight="1" s="103">
-      <c r="A23" s="107" t="inlineStr">
+      <c r="J22" s="101" t="n"/>
+      <c r="K22" s="101" t="n"/>
+      <c r="L22" s="101" t="n"/>
+      <c r="M22" s="101" t="n"/>
+      <c r="N22" s="101" t="n"/>
+      <c r="O22" s="101" t="n"/>
+      <c r="P22" s="101" t="n"/>
+      <c r="Q22" s="101" t="n"/>
+      <c r="R22" s="101" t="n"/>
+    </row>
+    <row r="23" ht="13.15" customHeight="1" s="91">
+      <c r="A23" s="103" t="inlineStr">
         <is>
           <t>Haag, Lorenz</t>
         </is>
       </c>
-      <c r="B23" s="110">
+      <c r="B23" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C23" s="108" t="n">
+      <c r="C23" s="104" t="n">
         <v>20</v>
       </c>
-      <c r="D23" s="108" t="n">
+      <c r="D23" s="104" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="108" t="n">
+      <c r="E23" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="108" t="n"/>
-      <c r="G23" s="108">
-        <f>SUM(C23:F23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="108">
-        <f>B23+G23</f>
-        <v/>
-      </c>
-      <c r="I23" s="112">
+      <c r="F23" s="104" t="n"/>
+      <c r="G23" s="104">
+        <f>C23+D23+E23+F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="104">
+        <f>G23+B23</f>
+        <v/>
+      </c>
+      <c r="I23" s="114">
         <f>IFERROR(LOOKUP(2,1/((B23&lt;$J$3:$R$3)*(H23&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J23" s="108" t="n"/>
-      <c r="K23" s="108" t="n"/>
-      <c r="L23" s="108" t="n"/>
-      <c r="M23" s="108" t="n"/>
-      <c r="N23" s="108" t="n"/>
-      <c r="O23" s="108" t="n"/>
-      <c r="P23" s="108" t="n"/>
-      <c r="Q23" s="108" t="n"/>
-      <c r="R23" s="108" t="n"/>
-    </row>
-    <row r="24" ht="13.2" customHeight="1" s="103">
-      <c r="A24" s="104" t="inlineStr">
+      <c r="J23" s="104" t="n"/>
+      <c r="K23" s="104" t="n"/>
+      <c r="L23" s="104" t="n"/>
+      <c r="M23" s="104" t="n"/>
+      <c r="N23" s="104" t="n"/>
+      <c r="O23" s="104" t="n"/>
+      <c r="P23" s="104" t="n"/>
+      <c r="Q23" s="104" t="n"/>
+      <c r="R23" s="104" t="n"/>
+    </row>
+    <row r="24" ht="13.15" customHeight="1" s="91">
+      <c r="A24" s="100" t="inlineStr">
         <is>
           <t>Haag, Marius</t>
         </is>
       </c>
-      <c r="B24" s="111">
+      <c r="B24" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C24" s="105" t="n">
+      <c r="C24" s="101" t="n">
         <v>18</v>
       </c>
-      <c r="D24" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="105" t="n">
+      <c r="D24" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="101" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="105" t="n"/>
-      <c r="G24" s="105">
-        <f>SUM(C24:F24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="105">
-        <f>B24+G24</f>
+      <c r="F24" s="101" t="n"/>
+      <c r="G24" s="101">
+        <f>C24+D24+E24+F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="101">
+        <f>G24+B24</f>
         <v/>
       </c>
       <c r="I24" s="113">
         <f>IFERROR(LOOKUP(2,1/((B24&lt;$J$3:$R$3)*(H24&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J24" s="105" t="n"/>
-      <c r="K24" s="105" t="n"/>
-      <c r="L24" s="105" t="n"/>
-      <c r="M24" s="105" t="n"/>
-      <c r="N24" s="105" t="n"/>
-      <c r="O24" s="105" t="n"/>
-      <c r="P24" s="105" t="n"/>
-      <c r="Q24" s="105" t="n"/>
-      <c r="R24" s="105" t="n"/>
-    </row>
-    <row r="25" ht="13.2" customHeight="1" s="103">
-      <c r="A25" s="107" t="inlineStr">
+      <c r="J24" s="101" t="n"/>
+      <c r="K24" s="101" t="n"/>
+      <c r="L24" s="101" t="n"/>
+      <c r="M24" s="101" t="n"/>
+      <c r="N24" s="101" t="n"/>
+      <c r="O24" s="101" t="n"/>
+      <c r="P24" s="101" t="n"/>
+      <c r="Q24" s="101" t="n"/>
+      <c r="R24" s="101" t="n"/>
+    </row>
+    <row r="25" ht="13.15" customHeight="1" s="91">
+      <c r="A25" s="103" t="inlineStr">
         <is>
           <t>Haas, Steffen</t>
         </is>
       </c>
-      <c r="B25" s="110">
+      <c r="B25" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C25" s="108" t="n">
+      <c r="C25" s="104" t="n">
         <v>8</v>
       </c>
-      <c r="D25" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="108" t="n">
+      <c r="D25" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="108" t="n"/>
-      <c r="G25" s="108">
-        <f>SUM(C25:F25)</f>
-        <v/>
-      </c>
-      <c r="H25" s="108">
-        <f>B25+G25</f>
-        <v/>
-      </c>
-      <c r="I25" s="112">
+      <c r="F25" s="104" t="n"/>
+      <c r="G25" s="104">
+        <f>C25+D25+E25+F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="104">
+        <f>G25+B25</f>
+        <v/>
+      </c>
+      <c r="I25" s="114">
         <f>IFERROR(LOOKUP(2,1/((B25&lt;$J$3:$R$3)*(H25&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J25" s="108" t="n"/>
-      <c r="K25" s="108" t="n"/>
-      <c r="L25" s="108" t="n"/>
-      <c r="M25" s="108" t="n"/>
-      <c r="N25" s="108" t="n"/>
-      <c r="O25" s="108" t="n"/>
-      <c r="P25" s="108" t="n"/>
-      <c r="Q25" s="108" t="n"/>
-      <c r="R25" s="108" t="n"/>
-    </row>
-    <row r="26" ht="13.2" customHeight="1" s="103">
-      <c r="A26" s="104" t="inlineStr">
+      <c r="J25" s="104" t="n"/>
+      <c r="K25" s="104" t="n"/>
+      <c r="L25" s="104" t="n"/>
+      <c r="M25" s="104" t="n"/>
+      <c r="N25" s="104" t="n"/>
+      <c r="O25" s="104" t="n"/>
+      <c r="P25" s="104" t="n"/>
+      <c r="Q25" s="104" t="n"/>
+      <c r="R25" s="104" t="n"/>
+    </row>
+    <row r="26" ht="13.15" customHeight="1" s="91">
+      <c r="A26" s="100" t="inlineStr">
         <is>
           <t>Heim, Moritz</t>
         </is>
       </c>
-      <c r="B26" s="111">
+      <c r="B26" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C26" s="105" t="n">
+      <c r="C26" s="101" t="n">
         <v>8</v>
       </c>
-      <c r="D26" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="105" t="n"/>
-      <c r="G26" s="105">
-        <f>SUM(C26:F26)</f>
-        <v/>
-      </c>
-      <c r="H26" s="105">
-        <f>B26+G26</f>
+      <c r="D26" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="101" t="n"/>
+      <c r="G26" s="101">
+        <f>C26+D26+E26+F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="101">
+        <f>G26+B26</f>
         <v/>
       </c>
       <c r="I26" s="113">
         <f>IFERROR(LOOKUP(2,1/((B26&lt;$J$3:$R$3)*(H26&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J26" s="105" t="n"/>
-      <c r="K26" s="105" t="n"/>
-      <c r="L26" s="105" t="n"/>
-      <c r="M26" s="105" t="n"/>
-      <c r="N26" s="105" t="n"/>
-      <c r="O26" s="105" t="n"/>
-      <c r="P26" s="105" t="n"/>
-      <c r="Q26" s="105" t="n"/>
-      <c r="R26" s="105" t="n"/>
-    </row>
-    <row r="27" ht="13.2" customHeight="1" s="103">
-      <c r="A27" s="108" t="inlineStr">
+      <c r="J26" s="101" t="n"/>
+      <c r="K26" s="101" t="n"/>
+      <c r="L26" s="101" t="n"/>
+      <c r="M26" s="101" t="n"/>
+      <c r="N26" s="101" t="n"/>
+      <c r="O26" s="101" t="n"/>
+      <c r="P26" s="101" t="n"/>
+      <c r="Q26" s="101" t="n"/>
+      <c r="R26" s="101" t="n"/>
+    </row>
+    <row r="27" ht="13.15" customHeight="1" s="91">
+      <c r="A27" s="103" t="inlineStr">
         <is>
           <t>Hoch, Philipp</t>
         </is>
       </c>
-      <c r="B27" s="110">
+      <c r="B27" s="104">
+        <f>'24-25'!H28</f>
+        <v/>
+      </c>
+      <c r="C27" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="104" t="n"/>
+      <c r="G27" s="104">
+        <f>C27+D27+E27+F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="104">
+        <f>G27+B27</f>
+        <v/>
+      </c>
+      <c r="I27" s="114">
+        <f>IFERROR(LOOKUP(2,1/((B27&lt;$J$3:$R$3)*(H27&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="104" t="n"/>
+      <c r="K27" s="104" t="n"/>
+      <c r="L27" s="104" t="n"/>
+      <c r="M27" s="104" t="n"/>
+      <c r="N27" s="104" t="n"/>
+      <c r="O27" s="104" t="n"/>
+      <c r="P27" s="104" t="n"/>
+      <c r="Q27" s="104" t="n"/>
+      <c r="R27" s="104" t="n"/>
+    </row>
+    <row r="28" ht="13.15" customHeight="1" s="91">
+      <c r="A28" s="101" t="inlineStr">
+        <is>
+          <t>Hornberger, Christian</t>
+        </is>
+      </c>
+      <c r="B28" s="101">
+        <f>'24-25'!H29</f>
+        <v/>
+      </c>
+      <c r="C28" s="101" t="n">
+        <v>21</v>
+      </c>
+      <c r="D28" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="101" t="n"/>
+      <c r="G28" s="101">
+        <f>C28+D28+E28+F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="101">
+        <f>G28+B28</f>
+        <v/>
+      </c>
+      <c r="I28" s="106">
+        <f>IFERROR(LOOKUP(2,1/((B28&lt;$J$3:$R$3)*(H28&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="101" t="n"/>
+      <c r="K28" s="101" t="n"/>
+      <c r="L28" s="101" t="n"/>
+      <c r="M28" s="101" t="n"/>
+      <c r="N28" s="101" t="n"/>
+      <c r="O28" s="101" t="n"/>
+      <c r="P28" s="101" t="n"/>
+      <c r="Q28" s="101" t="n"/>
+      <c r="R28" s="101" t="n"/>
+    </row>
+    <row r="29" ht="13.15" customHeight="1" s="91">
+      <c r="A29" s="103" t="inlineStr">
+        <is>
+          <t>Jauch, Heinrich</t>
+        </is>
+      </c>
+      <c r="B29" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C27" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="108" t="n"/>
-      <c r="G27" s="108">
-        <f>SUM(C27:F27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="108">
-        <f>B27+G27</f>
-        <v/>
-      </c>
-      <c r="I27" s="108">
-        <f>IFERROR(LOOKUP(2,1/((B27&lt;$J$3:$R$3)*(H27&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="108" t="n"/>
-      <c r="K27" s="108" t="n"/>
-      <c r="L27" s="108" t="n"/>
-      <c r="M27" s="108" t="n"/>
-      <c r="N27" s="108" t="n"/>
-      <c r="O27" s="108" t="n"/>
-      <c r="P27" s="108" t="n"/>
-      <c r="Q27" s="108" t="n"/>
-      <c r="R27" s="108" t="n"/>
-    </row>
-    <row r="28" ht="13.2" customHeight="1" s="103">
-      <c r="A28" s="104" t="inlineStr">
-        <is>
-          <t>Hornberger, Christian</t>
-        </is>
-      </c>
-      <c r="B28" s="105">
-        <f>'24-25'!H28</f>
-        <v/>
-      </c>
-      <c r="C28" s="105" t="n">
-        <v>21</v>
-      </c>
-      <c r="D28" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="105" t="n">
-        <v>6</v>
-      </c>
-      <c r="F28" s="105" t="n"/>
-      <c r="G28" s="105">
-        <f>SUM(C28:F28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="105">
-        <f>B28+G28</f>
-        <v/>
-      </c>
-      <c r="I28" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B28&lt;$J$3:$R$3)*(H28&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="105" t="n"/>
-      <c r="K28" s="105" t="n"/>
-      <c r="L28" s="105" t="n"/>
-      <c r="M28" s="105" t="n"/>
-      <c r="N28" s="105" t="n"/>
-      <c r="O28" s="105" t="n"/>
-      <c r="P28" s="105" t="n"/>
-      <c r="Q28" s="105" t="n"/>
-      <c r="R28" s="105" t="n"/>
-    </row>
-    <row r="29" ht="13.2" customHeight="1" s="103">
-      <c r="A29" s="107" t="inlineStr">
-        <is>
-          <t>Jauch, Heinrich</t>
-        </is>
-      </c>
-      <c r="B29" s="110">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C29" s="108" t="n">
+      <c r="C29" s="104" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="108" t="n"/>
-      <c r="G29" s="108">
-        <f>SUM(C29:F29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="108">
-        <f>B29+G29</f>
-        <v/>
-      </c>
-      <c r="I29" s="112">
+      <c r="D29" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="104" t="n"/>
+      <c r="G29" s="104">
+        <f>C29+D29+E29+F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="104">
+        <f>G29+B29</f>
+        <v/>
+      </c>
+      <c r="I29" s="114">
         <f>IFERROR(LOOKUP(2,1/((B29&lt;$J$3:$R$3)*(H29&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J29" s="108" t="n"/>
-      <c r="K29" s="108" t="n"/>
-      <c r="L29" s="108" t="n"/>
-      <c r="M29" s="108" t="n"/>
-      <c r="N29" s="108" t="n"/>
-      <c r="O29" s="108" t="n"/>
-      <c r="P29" s="108" t="n"/>
-      <c r="Q29" s="108" t="n"/>
-      <c r="R29" s="108" t="n"/>
-    </row>
-    <row r="30" ht="13.2" customHeight="1" s="103">
-      <c r="A30" s="104" t="inlineStr">
+      <c r="J29" s="104" t="n"/>
+      <c r="K29" s="104" t="n"/>
+      <c r="L29" s="104" t="n"/>
+      <c r="M29" s="104" t="n"/>
+      <c r="N29" s="104" t="n"/>
+      <c r="O29" s="104" t="n"/>
+      <c r="P29" s="104" t="n"/>
+      <c r="Q29" s="104" t="n"/>
+      <c r="R29" s="104" t="n"/>
+    </row>
+    <row r="30" ht="13.15" customHeight="1" s="91">
+      <c r="A30" s="100" t="inlineStr">
         <is>
           <t>Katzer, Florian</t>
         </is>
       </c>
-      <c r="B30" s="111">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C30" s="105" t="n">
+      <c r="B30" s="101">
+        <f>'24-25'!H23</f>
+        <v/>
+      </c>
+      <c r="C30" s="101" t="n">
         <v>4</v>
       </c>
-      <c r="D30" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="105" t="n">
+      <c r="D30" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="105" t="n"/>
-      <c r="G30" s="105">
-        <f>SUM(C30:F30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="105">
-        <f>B30+G30</f>
+      <c r="F30" s="101" t="n"/>
+      <c r="G30" s="101">
+        <f>C30+D30+E30+F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="101">
+        <f>G30+B30</f>
         <v/>
       </c>
       <c r="I30" s="113">
         <f>IFERROR(LOOKUP(2,1/((B30&lt;$J$3:$R$3)*(H30&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J30" s="105" t="n"/>
-      <c r="K30" s="105" t="n"/>
-      <c r="L30" s="105" t="n"/>
-      <c r="M30" s="105" t="n"/>
-      <c r="N30" s="105" t="n"/>
-      <c r="O30" s="105" t="n"/>
-      <c r="P30" s="105" t="n"/>
-      <c r="Q30" s="105" t="n"/>
-      <c r="R30" s="105" t="n"/>
-    </row>
-    <row r="31" ht="13.2" customHeight="1" s="103">
-      <c r="A31" s="107" t="inlineStr">
+      <c r="J30" s="101" t="n"/>
+      <c r="K30" s="101" t="n"/>
+      <c r="L30" s="101" t="n"/>
+      <c r="M30" s="101" t="n"/>
+      <c r="N30" s="101" t="n"/>
+      <c r="O30" s="101" t="n"/>
+      <c r="P30" s="101" t="n"/>
+      <c r="Q30" s="101" t="n"/>
+      <c r="R30" s="101" t="n"/>
+    </row>
+    <row r="31" ht="13.15" customHeight="1" s="91">
+      <c r="A31" s="103" t="inlineStr">
         <is>
           <t>Klukas, Pascal</t>
         </is>
       </c>
-      <c r="B31" s="108">
-        <f>'24-25'!H31</f>
-        <v/>
-      </c>
-      <c r="C31" s="108" t="n">
+      <c r="B31" s="104">
+        <f>'24-25'!H32</f>
+        <v/>
+      </c>
+      <c r="C31" s="104" t="n">
         <v>19</v>
       </c>
-      <c r="D31" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="108" t="n">
+      <c r="D31" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="104" t="n">
         <v>7</v>
       </c>
-      <c r="F31" s="108" t="n"/>
-      <c r="G31" s="108">
-        <f>SUM(C31:F31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="108">
-        <f>B31+G31</f>
-        <v/>
-      </c>
-      <c r="I31" s="112">
+      <c r="F31" s="104" t="n"/>
+      <c r="G31" s="104">
+        <f>C31+D31+E31+F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="104">
+        <f>G31+B31</f>
+        <v/>
+      </c>
+      <c r="I31" s="114">
         <f>IFERROR(LOOKUP(2,1/((B31&lt;$J$3:$R$3)*(H31&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J31" s="108" t="n"/>
-      <c r="K31" s="108" t="n"/>
-      <c r="L31" s="108" t="n"/>
-      <c r="M31" s="108" t="n"/>
-      <c r="N31" s="108" t="n"/>
-      <c r="O31" s="108" t="n"/>
-      <c r="P31" s="108" t="n"/>
-      <c r="Q31" s="108" t="n"/>
-      <c r="R31" s="108" t="n"/>
-    </row>
-    <row r="32" ht="13.2" customHeight="1" s="103">
-      <c r="A32" s="104" t="inlineStr">
+      <c r="J31" s="104" t="n"/>
+      <c r="K31" s="104" t="n"/>
+      <c r="L31" s="104" t="n"/>
+      <c r="M31" s="104" t="n"/>
+      <c r="N31" s="104" t="n"/>
+      <c r="O31" s="104" t="n"/>
+      <c r="P31" s="104" t="n"/>
+      <c r="Q31" s="104" t="n"/>
+      <c r="R31" s="104" t="n"/>
+    </row>
+    <row r="32" ht="13.15" customHeight="1" s="91">
+      <c r="A32" s="100" t="inlineStr">
         <is>
           <t>Krohn, Florian</t>
         </is>
       </c>
-      <c r="B32" s="111">
+      <c r="B32" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C32" s="105" t="n">
+      <c r="C32" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="105" t="n"/>
-      <c r="G32" s="105">
-        <f>SUM(C32:F32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="105">
-        <f>B32+G32</f>
+      <c r="D32" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="101" t="n"/>
+      <c r="G32" s="101">
+        <f>C32+D32+E32+F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="101">
+        <f>G32+B32</f>
         <v/>
       </c>
       <c r="I32" s="113">
         <f>IFERROR(LOOKUP(2,1/((B32&lt;$J$3:$R$3)*(H32&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J32" s="105" t="n"/>
-      <c r="K32" s="105" t="n"/>
-      <c r="L32" s="105" t="n"/>
-      <c r="M32" s="105" t="n"/>
-      <c r="N32" s="105" t="n"/>
-      <c r="O32" s="105" t="n"/>
-      <c r="P32" s="105" t="n"/>
-      <c r="Q32" s="105" t="n"/>
-      <c r="R32" s="105" t="n"/>
-    </row>
-    <row r="33" ht="13.2" customHeight="1" s="103">
-      <c r="A33" s="107" t="inlineStr">
+      <c r="J32" s="101" t="n"/>
+      <c r="K32" s="101" t="n"/>
+      <c r="L32" s="101" t="n"/>
+      <c r="M32" s="101" t="n"/>
+      <c r="N32" s="101" t="n"/>
+      <c r="O32" s="101" t="n"/>
+      <c r="P32" s="101" t="n"/>
+      <c r="Q32" s="101" t="n"/>
+      <c r="R32" s="101" t="n"/>
+    </row>
+    <row r="33" ht="13.15" customHeight="1" s="91">
+      <c r="A33" s="103" t="inlineStr">
         <is>
           <t>Kuner, Andreas</t>
         </is>
       </c>
-      <c r="B33" s="108">
-        <f>'24-25'!H33</f>
-        <v/>
-      </c>
-      <c r="C33" s="108" t="n">
+      <c r="B33" s="104">
+        <f>'24-25'!H34</f>
+        <v/>
+      </c>
+      <c r="C33" s="104" t="n">
         <v>20</v>
       </c>
-      <c r="D33" s="108" t="n">
+      <c r="D33" s="104" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="108" t="n">
+      <c r="E33" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="F33" s="108" t="n"/>
-      <c r="G33" s="108">
-        <f>SUM(C33:F33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="108">
-        <f>B33+G33</f>
-        <v/>
-      </c>
-      <c r="I33" s="112">
+      <c r="F33" s="104" t="n"/>
+      <c r="G33" s="104">
+        <f>C33+D33+E33+F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="104">
+        <f>G33+B33</f>
+        <v/>
+      </c>
+      <c r="I33" s="114">
         <f>IFERROR(LOOKUP(2,1/((B33&lt;$J$3:$R$3)*(H33&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J33" s="108" t="n"/>
-      <c r="K33" s="108" t="n"/>
-      <c r="L33" s="108" t="n"/>
-      <c r="M33" s="108" t="n"/>
-      <c r="N33" s="108" t="n"/>
-      <c r="O33" s="108" t="n"/>
-      <c r="P33" s="108" t="n"/>
-      <c r="Q33" s="108" t="n"/>
-      <c r="R33" s="108" t="n"/>
-    </row>
-    <row r="34" ht="13.2" customHeight="1" s="103">
-      <c r="A34" s="104" t="inlineStr">
+      <c r="J33" s="104" t="n"/>
+      <c r="K33" s="104" t="n"/>
+      <c r="L33" s="104" t="n"/>
+      <c r="M33" s="104" t="n"/>
+      <c r="N33" s="104" t="n"/>
+      <c r="O33" s="104" t="n"/>
+      <c r="P33" s="104" t="n"/>
+      <c r="Q33" s="104" t="n"/>
+      <c r="R33" s="104" t="n"/>
+    </row>
+    <row r="34" ht="13.15" customHeight="1" s="91">
+      <c r="A34" s="100" t="inlineStr">
         <is>
           <t>Kunz, Holger</t>
         </is>
       </c>
-      <c r="B34" s="105">
-        <f>'24-25'!H34</f>
-        <v/>
-      </c>
-      <c r="C34" s="105" t="n">
+      <c r="B34" s="101">
+        <f>'24-25'!H35</f>
+        <v/>
+      </c>
+      <c r="C34" s="101" t="n">
         <v>17</v>
       </c>
-      <c r="D34" s="105" t="n">
+      <c r="D34" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="105" t="n">
+      <c r="E34" s="101" t="n">
         <v>7</v>
       </c>
-      <c r="F34" s="105" t="n"/>
-      <c r="G34" s="105">
-        <f>SUM(C34:F34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="105">
-        <f>B34+G34</f>
+      <c r="F34" s="101" t="n"/>
+      <c r="G34" s="101">
+        <f>C34+D34+E34+F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="101">
+        <f>G34+B34</f>
         <v/>
       </c>
       <c r="I34" s="113">
         <f>IFERROR(LOOKUP(2,1/((B34&lt;$J$3:$R$3)*(H34&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J34" s="105" t="n"/>
-      <c r="K34" s="105" t="n"/>
-      <c r="L34" s="105" t="n"/>
-      <c r="M34" s="105" t="n"/>
-      <c r="N34" s="105" t="n"/>
-      <c r="O34" s="105" t="n"/>
-      <c r="P34" s="105" t="n"/>
-      <c r="Q34" s="105" t="n"/>
-      <c r="R34" s="105" t="n"/>
-    </row>
-    <row r="35" ht="13.2" customHeight="1" s="103">
-      <c r="A35" s="107" t="inlineStr">
+      <c r="J34" s="101" t="n"/>
+      <c r="K34" s="101" t="n"/>
+      <c r="L34" s="101" t="n"/>
+      <c r="M34" s="101" t="n"/>
+      <c r="N34" s="101" t="n"/>
+      <c r="O34" s="101" t="n"/>
+      <c r="P34" s="101" t="n"/>
+      <c r="Q34" s="101" t="n"/>
+      <c r="R34" s="101" t="n"/>
+    </row>
+    <row r="35" ht="13.15" customHeight="1" s="91">
+      <c r="A35" s="103" t="inlineStr">
         <is>
           <t>Linder, Andreas</t>
         </is>
       </c>
-      <c r="B35" s="108">
-        <f>'24-25'!H36</f>
-        <v/>
-      </c>
-      <c r="C35" s="108" t="n">
+      <c r="B35" s="104">
+        <f>'24-25'!H37</f>
+        <v/>
+      </c>
+      <c r="C35" s="104" t="n">
         <v>12</v>
       </c>
-      <c r="D35" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="108" t="n">
+      <c r="D35" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="F35" s="108" t="n"/>
-      <c r="G35" s="108">
-        <f>SUM(C35:F35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="108">
-        <f>B35+G35</f>
-        <v/>
-      </c>
-      <c r="I35" s="112">
+      <c r="F35" s="104" t="n"/>
+      <c r="G35" s="104">
+        <f>C35+D35+E35+F35</f>
+        <v/>
+      </c>
+      <c r="H35" s="104">
+        <f>G35+B35</f>
+        <v/>
+      </c>
+      <c r="I35" s="114">
         <f>IFERROR(LOOKUP(2,1/((B35&lt;$J$3:$R$3)*(H35&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J35" s="108" t="n"/>
-      <c r="K35" s="108" t="n"/>
-      <c r="L35" s="108" t="n"/>
-      <c r="M35" s="108" t="n"/>
-      <c r="N35" s="108" t="n"/>
-      <c r="O35" s="108" t="n"/>
-      <c r="P35" s="108" t="n"/>
-      <c r="Q35" s="108" t="n"/>
-      <c r="R35" s="108" t="n"/>
-    </row>
-    <row r="36" ht="13.2" customHeight="1" s="103">
-      <c r="A36" s="104" t="inlineStr">
+      <c r="J35" s="104" t="n"/>
+      <c r="K35" s="104" t="n"/>
+      <c r="L35" s="104" t="n"/>
+      <c r="M35" s="104" t="n"/>
+      <c r="N35" s="104" t="n"/>
+      <c r="O35" s="104" t="n"/>
+      <c r="P35" s="104" t="n"/>
+      <c r="Q35" s="104" t="n"/>
+      <c r="R35" s="104" t="n"/>
+    </row>
+    <row r="36" ht="13.15" customHeight="1" s="91">
+      <c r="A36" s="100" t="inlineStr">
         <is>
           <t>Lobert, Marius</t>
         </is>
       </c>
-      <c r="B36" s="105">
-        <f>'24-25'!H37</f>
-        <v/>
-      </c>
-      <c r="C36" s="105" t="n">
+      <c r="B36" s="101">
+        <f>'24-25'!H38</f>
+        <v/>
+      </c>
+      <c r="C36" s="101" t="n">
         <v>13</v>
       </c>
-      <c r="D36" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="105" t="n">
+      <c r="D36" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="101" t="n">
         <v>6</v>
       </c>
-      <c r="F36" s="105" t="n"/>
-      <c r="G36" s="105">
-        <f>SUM(C36:F36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="105">
-        <f>B36+G36</f>
+      <c r="F36" s="101" t="n"/>
+      <c r="G36" s="101">
+        <f>C36+D36+E36+F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="101">
+        <f>G36+B36</f>
         <v/>
       </c>
       <c r="I36" s="113">
         <f>IFERROR(LOOKUP(2,1/((B36&lt;$J$3:$R$3)*(H36&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J36" s="105" t="n"/>
-      <c r="K36" s="105" t="n"/>
-      <c r="L36" s="105" t="n"/>
-      <c r="M36" s="105" t="n"/>
-      <c r="N36" s="105" t="n"/>
-      <c r="O36" s="105" t="n"/>
-      <c r="P36" s="105" t="n"/>
-      <c r="Q36" s="105" t="n"/>
-      <c r="R36" s="105" t="n"/>
-    </row>
-    <row r="37" ht="13.2" customHeight="1" s="103">
-      <c r="A37" s="107" t="inlineStr">
+      <c r="J36" s="101" t="n"/>
+      <c r="K36" s="101" t="n"/>
+      <c r="L36" s="101" t="n"/>
+      <c r="M36" s="101" t="n"/>
+      <c r="N36" s="101" t="n"/>
+      <c r="O36" s="101" t="n"/>
+      <c r="P36" s="101" t="n"/>
+      <c r="Q36" s="101" t="n"/>
+      <c r="R36" s="101" t="n"/>
+    </row>
+    <row r="37" ht="13.15" customHeight="1" s="91">
+      <c r="A37" s="103" t="inlineStr">
         <is>
           <t>Löffler, Marius</t>
         </is>
       </c>
-      <c r="B37" s="108">
-        <f>'24-25'!H38</f>
-        <v/>
-      </c>
-      <c r="C37" s="108" t="n">
+      <c r="B37" s="104">
+        <f>'24-25'!H39</f>
+        <v/>
+      </c>
+      <c r="C37" s="104" t="n">
         <v>18</v>
       </c>
-      <c r="D37" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="108" t="n">
+      <c r="D37" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="F37" s="108" t="n"/>
-      <c r="G37" s="108">
-        <f>SUM(C37:F37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="108">
-        <f>B37+G37</f>
-        <v/>
-      </c>
-      <c r="I37" s="112">
+      <c r="F37" s="104" t="n"/>
+      <c r="G37" s="104">
+        <f>C37+D37+E37+F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="104">
+        <f>G37+B37</f>
+        <v/>
+      </c>
+      <c r="I37" s="114">
         <f>IFERROR(LOOKUP(2,1/((B37&lt;$J$3:$R$3)*(H37&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J37" s="108" t="n"/>
-      <c r="K37" s="108" t="n"/>
-      <c r="L37" s="108" t="n"/>
-      <c r="M37" s="108" t="n"/>
-      <c r="N37" s="108" t="n"/>
-      <c r="O37" s="108" t="n"/>
-      <c r="P37" s="108" t="n"/>
-      <c r="Q37" s="108" t="n"/>
-      <c r="R37" s="108" t="n"/>
-    </row>
-    <row r="38" ht="13.2" customHeight="1" s="103">
-      <c r="A38" s="104" t="inlineStr">
+      <c r="J37" s="104" t="n"/>
+      <c r="K37" s="104" t="n"/>
+      <c r="L37" s="104" t="n"/>
+      <c r="M37" s="104" t="n"/>
+      <c r="N37" s="104" t="n"/>
+      <c r="O37" s="104" t="n"/>
+      <c r="P37" s="104" t="n"/>
+      <c r="Q37" s="104" t="n"/>
+      <c r="R37" s="104" t="n"/>
+    </row>
+    <row r="38" ht="13.15" customHeight="1" s="91">
+      <c r="A38" s="100" t="inlineStr">
         <is>
           <t>Mager, Elias</t>
         </is>
       </c>
-      <c r="B38" s="111">
+      <c r="B38" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C38" s="105" t="n">
+      <c r="C38" s="101" t="n">
         <v>13</v>
       </c>
-      <c r="D38" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="105" t="n">
+      <c r="D38" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="101" t="n">
         <v>5</v>
       </c>
-      <c r="F38" s="105" t="n"/>
-      <c r="G38" s="105">
-        <f>SUM(C38:F38)</f>
-        <v/>
-      </c>
-      <c r="H38" s="105">
-        <f>B38+G38</f>
+      <c r="F38" s="101" t="n"/>
+      <c r="G38" s="101">
+        <f>C38+D38+E38+F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="101">
+        <f>G38+B38</f>
         <v/>
       </c>
       <c r="I38" s="113">
         <f>IFERROR(LOOKUP(2,1/((B38&lt;$J$3:$R$3)*(H38&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J38" s="105" t="n"/>
-      <c r="K38" s="105" t="n"/>
-      <c r="L38" s="105" t="n"/>
-      <c r="M38" s="105" t="n"/>
-      <c r="N38" s="105" t="n"/>
-      <c r="O38" s="105" t="n"/>
-      <c r="P38" s="105" t="n"/>
-      <c r="Q38" s="105" t="n"/>
-      <c r="R38" s="105" t="n"/>
-    </row>
-    <row r="39" ht="13.2" customHeight="1" s="103">
-      <c r="A39" s="107" t="inlineStr">
+      <c r="J38" s="101" t="n"/>
+      <c r="K38" s="101" t="n"/>
+      <c r="L38" s="101" t="n"/>
+      <c r="M38" s="101" t="n"/>
+      <c r="N38" s="101" t="n"/>
+      <c r="O38" s="101" t="n"/>
+      <c r="P38" s="101" t="n"/>
+      <c r="Q38" s="101" t="n"/>
+      <c r="R38" s="101" t="n"/>
+    </row>
+    <row r="39" ht="13.15" customHeight="1" s="91">
+      <c r="A39" s="103" t="inlineStr">
         <is>
           <t>Mager, Max</t>
         </is>
       </c>
-      <c r="B39" s="110">
+      <c r="B39" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C39" s="108" t="n">
+      <c r="C39" s="104" t="n">
         <v>19</v>
       </c>
-      <c r="D39" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="108" t="n">
+      <c r="D39" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="104" t="n">
         <v>9</v>
       </c>
-      <c r="F39" s="108" t="n"/>
-      <c r="G39" s="108">
-        <f>SUM(C39:F39)</f>
-        <v/>
-      </c>
-      <c r="H39" s="108">
-        <f>B39+G39</f>
-        <v/>
-      </c>
-      <c r="I39" s="112">
+      <c r="F39" s="104" t="n"/>
+      <c r="G39" s="104">
+        <f>C39+D39+E39+F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="104">
+        <f>G39+B39</f>
+        <v/>
+      </c>
+      <c r="I39" s="114">
         <f>IFERROR(LOOKUP(2,1/((B39&lt;$J$3:$R$3)*(H39&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J39" s="108" t="n"/>
-      <c r="K39" s="108" t="n"/>
-      <c r="L39" s="108" t="n"/>
-      <c r="M39" s="108" t="n"/>
-      <c r="N39" s="108" t="n"/>
-      <c r="O39" s="108" t="n"/>
-      <c r="P39" s="108" t="n"/>
-      <c r="Q39" s="108" t="n"/>
-      <c r="R39" s="108" t="n"/>
-    </row>
-    <row r="40" ht="13.2" customHeight="1" s="103">
-      <c r="A40" s="104" t="inlineStr">
+      <c r="J39" s="104" t="n"/>
+      <c r="K39" s="104" t="n"/>
+      <c r="L39" s="104" t="n"/>
+      <c r="M39" s="104" t="n"/>
+      <c r="N39" s="104" t="n"/>
+      <c r="O39" s="104" t="n"/>
+      <c r="P39" s="104" t="n"/>
+      <c r="Q39" s="104" t="n"/>
+      <c r="R39" s="104" t="n"/>
+    </row>
+    <row r="40" ht="13.15" customHeight="1" s="91">
+      <c r="A40" s="100" t="inlineStr">
         <is>
           <t>Marte, Marvin</t>
         </is>
       </c>
-      <c r="B40" s="111">
+      <c r="B40" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C40" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="105" t="n">
+      <c r="C40" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="105" t="n"/>
-      <c r="G40" s="105">
-        <f>SUM(C40:F40)</f>
-        <v/>
-      </c>
-      <c r="H40" s="105">
-        <f>B40+G40</f>
+      <c r="F40" s="101" t="n"/>
+      <c r="G40" s="101">
+        <f>C40+D40+E40+F40</f>
+        <v/>
+      </c>
+      <c r="H40" s="101">
+        <f>G40+B40</f>
         <v/>
       </c>
       <c r="I40" s="113">
         <f>IFERROR(LOOKUP(2,1/((B40&lt;$J$3:$R$3)*(H40&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J40" s="105" t="n"/>
-      <c r="K40" s="105" t="n"/>
-      <c r="L40" s="105" t="n"/>
-      <c r="M40" s="105" t="n"/>
-      <c r="N40" s="105" t="n"/>
-      <c r="O40" s="105" t="n"/>
-      <c r="P40" s="105" t="n"/>
-      <c r="Q40" s="105" t="n"/>
-      <c r="R40" s="105" t="n"/>
-    </row>
-    <row r="41" ht="13.2" customHeight="1" s="103">
-      <c r="A41" s="107" t="inlineStr">
+      <c r="J40" s="101" t="n"/>
+      <c r="K40" s="101" t="n"/>
+      <c r="L40" s="101" t="n"/>
+      <c r="M40" s="101" t="n"/>
+      <c r="N40" s="101" t="n"/>
+      <c r="O40" s="101" t="n"/>
+      <c r="P40" s="101" t="n"/>
+      <c r="Q40" s="101" t="n"/>
+      <c r="R40" s="101" t="n"/>
+    </row>
+    <row r="41" ht="13.15" customHeight="1" s="91">
+      <c r="A41" s="103" t="inlineStr">
         <is>
           <t>Mauch, Nico</t>
         </is>
       </c>
-      <c r="B41" s="110">
+      <c r="B41" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C41" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="108" t="n"/>
-      <c r="G41" s="108">
-        <f>SUM(C41:F41)</f>
-        <v/>
-      </c>
-      <c r="H41" s="108">
-        <f>B41+G41</f>
-        <v/>
-      </c>
-      <c r="I41" s="112">
+      <c r="C41" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="104" t="n"/>
+      <c r="G41" s="104">
+        <f>C41+D41+E41+F41</f>
+        <v/>
+      </c>
+      <c r="H41" s="104">
+        <f>G41+B41</f>
+        <v/>
+      </c>
+      <c r="I41" s="114">
         <f>IFERROR(LOOKUP(2,1/((B41&lt;$J$3:$R$3)*(H41&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J41" s="108" t="n"/>
-      <c r="K41" s="108" t="n"/>
-      <c r="L41" s="108" t="n"/>
-      <c r="M41" s="108" t="n"/>
-      <c r="N41" s="108" t="n"/>
-      <c r="O41" s="108" t="n"/>
-      <c r="P41" s="108" t="n"/>
-      <c r="Q41" s="108" t="n"/>
-      <c r="R41" s="108" t="n"/>
-    </row>
-    <row r="42" ht="13.2" customHeight="1" s="103">
-      <c r="A42" s="104" t="inlineStr">
+      <c r="J41" s="104" t="n"/>
+      <c r="K41" s="104" t="n"/>
+      <c r="L41" s="104" t="n"/>
+      <c r="M41" s="104" t="n"/>
+      <c r="N41" s="104" t="n"/>
+      <c r="O41" s="104" t="n"/>
+      <c r="P41" s="104" t="n"/>
+      <c r="Q41" s="104" t="n"/>
+      <c r="R41" s="104" t="n"/>
+    </row>
+    <row r="42" ht="13.15" customHeight="1" s="91">
+      <c r="A42" s="100" t="inlineStr">
         <is>
           <t>Moosmann, Jakob</t>
         </is>
       </c>
-      <c r="B42" s="111">
+      <c r="B42" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C42" s="105" t="n">
+      <c r="C42" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="D42" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="105" t="n"/>
-      <c r="G42" s="105">
-        <f>SUM(C42:F42)</f>
-        <v/>
-      </c>
-      <c r="H42" s="105">
-        <f>B42+G42</f>
+      <c r="D42" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="101" t="n"/>
+      <c r="G42" s="101">
+        <f>C42+D42+E42+F42</f>
+        <v/>
+      </c>
+      <c r="H42" s="101">
+        <f>G42+B42</f>
         <v/>
       </c>
       <c r="I42" s="113">
         <f>IFERROR(LOOKUP(2,1/((B42&lt;$J$3:$R$3)*(H42&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J42" s="105" t="n"/>
-      <c r="K42" s="105" t="n"/>
-      <c r="L42" s="105" t="n"/>
-      <c r="M42" s="105" t="n"/>
-      <c r="N42" s="105" t="n"/>
-      <c r="O42" s="105" t="n"/>
-      <c r="P42" s="105" t="n"/>
-      <c r="Q42" s="105" t="n"/>
-      <c r="R42" s="105" t="n"/>
-    </row>
-    <row r="43" ht="13.2" customHeight="1" s="103">
-      <c r="A43" s="107" t="inlineStr">
+      <c r="J42" s="101" t="n"/>
+      <c r="K42" s="101" t="n"/>
+      <c r="L42" s="101" t="n"/>
+      <c r="M42" s="101" t="n"/>
+      <c r="N42" s="101" t="n"/>
+      <c r="O42" s="101" t="n"/>
+      <c r="P42" s="101" t="n"/>
+      <c r="Q42" s="101" t="n"/>
+      <c r="R42" s="101" t="n"/>
+    </row>
+    <row r="43" ht="13.15" customHeight="1" s="91">
+      <c r="A43" s="103" t="inlineStr">
         <is>
           <t>Müller, Moritz</t>
         </is>
       </c>
-      <c r="B43" s="108">
-        <f>'24-25'!H41</f>
-        <v/>
-      </c>
-      <c r="C43" s="108" t="n">
+      <c r="B43" s="104">
+        <f>'24-25'!H42</f>
+        <v/>
+      </c>
+      <c r="C43" s="104" t="n">
         <v>18</v>
       </c>
-      <c r="D43" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="108" t="n">
+      <c r="D43" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="F43" s="108" t="n"/>
-      <c r="G43" s="108">
-        <f>SUM(C43:F43)</f>
-        <v/>
-      </c>
-      <c r="H43" s="108">
-        <f>B43+G43</f>
-        <v/>
-      </c>
-      <c r="I43" s="112">
+      <c r="F43" s="104" t="n"/>
+      <c r="G43" s="104">
+        <f>C43+D43+E43+F43</f>
+        <v/>
+      </c>
+      <c r="H43" s="104">
+        <f>G43+B43</f>
+        <v/>
+      </c>
+      <c r="I43" s="114">
         <f>IFERROR(LOOKUP(2,1/((B43&lt;$J$3:$R$3)*(H43&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J43" s="108" t="n"/>
-      <c r="K43" s="108" t="n"/>
-      <c r="L43" s="108" t="n"/>
-      <c r="M43" s="108" t="n"/>
-      <c r="N43" s="108" t="n"/>
-      <c r="O43" s="108" t="n"/>
-      <c r="P43" s="108" t="n"/>
-      <c r="Q43" s="108" t="n"/>
-      <c r="R43" s="108" t="n"/>
-    </row>
-    <row r="44" ht="13.2" customHeight="1" s="103">
-      <c r="A44" s="104" t="inlineStr">
+      <c r="J43" s="104" t="n"/>
+      <c r="K43" s="104" t="n"/>
+      <c r="L43" s="104" t="n"/>
+      <c r="M43" s="104" t="n"/>
+      <c r="N43" s="104" t="n"/>
+      <c r="O43" s="104" t="n"/>
+      <c r="P43" s="104" t="n"/>
+      <c r="Q43" s="104" t="n"/>
+      <c r="R43" s="104" t="n"/>
+    </row>
+    <row r="44" ht="13.15" customHeight="1" s="91">
+      <c r="A44" s="100" t="inlineStr">
         <is>
           <t>Müllhäuser, Florian</t>
         </is>
       </c>
-      <c r="B44" s="111">
+      <c r="B44" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C44" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="105" t="n"/>
-      <c r="G44" s="105">
-        <f>SUM(C44:F44)</f>
-        <v/>
-      </c>
-      <c r="H44" s="105">
-        <f>B44+G44</f>
+      <c r="C44" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="101" t="n"/>
+      <c r="G44" s="101">
+        <f>C44+D44+E44+F44</f>
+        <v/>
+      </c>
+      <c r="H44" s="101">
+        <f>G44+B44</f>
         <v/>
       </c>
       <c r="I44" s="113">
         <f>IFERROR(LOOKUP(2,1/((B44&lt;$J$3:$R$3)*(H44&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J44" s="105" t="n"/>
-      <c r="K44" s="105" t="n"/>
-      <c r="L44" s="105" t="n"/>
-      <c r="M44" s="105" t="n"/>
-      <c r="N44" s="105" t="n"/>
-      <c r="O44" s="105" t="n"/>
-      <c r="P44" s="105" t="n"/>
-      <c r="Q44" s="105" t="n"/>
-      <c r="R44" s="105" t="n"/>
-    </row>
-    <row r="45" ht="13.2" customHeight="1" s="103">
-      <c r="A45" s="107" t="inlineStr">
+      <c r="J44" s="101" t="n"/>
+      <c r="K44" s="101" t="n"/>
+      <c r="L44" s="101" t="n"/>
+      <c r="M44" s="101" t="n"/>
+      <c r="N44" s="101" t="n"/>
+      <c r="O44" s="101" t="n"/>
+      <c r="P44" s="101" t="n"/>
+      <c r="Q44" s="101" t="n"/>
+      <c r="R44" s="101" t="n"/>
+    </row>
+    <row r="45" ht="13.15" customHeight="1" s="91">
+      <c r="A45" s="103" t="inlineStr">
         <is>
           <t>Müllhäuser, Nils</t>
         </is>
       </c>
-      <c r="B45" s="110">
+      <c r="B45" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C45" s="108" t="n">
+      <c r="C45" s="104" t="n">
         <v>13</v>
       </c>
-      <c r="D45" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="108" t="n">
+      <c r="D45" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="104" t="n">
         <v>5</v>
       </c>
-      <c r="F45" s="108" t="n"/>
-      <c r="G45" s="108">
-        <f>SUM(C45:F45)</f>
-        <v/>
-      </c>
-      <c r="H45" s="108">
-        <f>B45+G45</f>
-        <v/>
-      </c>
-      <c r="I45" s="112">
+      <c r="F45" s="104" t="n"/>
+      <c r="G45" s="104">
+        <f>C45+D45+E45+F45</f>
+        <v/>
+      </c>
+      <c r="H45" s="104">
+        <f>G45+B45</f>
+        <v/>
+      </c>
+      <c r="I45" s="114">
         <f>IFERROR(LOOKUP(2,1/((B45&lt;$J$3:$R$3)*(H45&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J45" s="108" t="n"/>
-      <c r="K45" s="108" t="n"/>
-      <c r="L45" s="108" t="n"/>
-      <c r="M45" s="108" t="n"/>
-      <c r="N45" s="108" t="n"/>
-      <c r="O45" s="108" t="n"/>
-      <c r="P45" s="108" t="n"/>
-      <c r="Q45" s="108" t="n"/>
-      <c r="R45" s="108" t="n"/>
-    </row>
-    <row r="46" ht="13.2" customHeight="1" s="103">
-      <c r="A46" s="104" t="inlineStr">
+      <c r="J45" s="104" t="n"/>
+      <c r="K45" s="104" t="n"/>
+      <c r="L45" s="104" t="n"/>
+      <c r="M45" s="104" t="n"/>
+      <c r="N45" s="104" t="n"/>
+      <c r="O45" s="104" t="n"/>
+      <c r="P45" s="104" t="n"/>
+      <c r="Q45" s="104" t="n"/>
+      <c r="R45" s="104" t="n"/>
+    </row>
+    <row r="46" ht="13.15" customHeight="1" s="91">
+      <c r="A46" s="100" t="inlineStr">
         <is>
           <t>Pforte, Lukas</t>
         </is>
       </c>
-      <c r="B46" s="111">
+      <c r="B46" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C46" s="105" t="n">
+      <c r="C46" s="101" t="n">
         <v>5</v>
       </c>
-      <c r="D46" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="105" t="n"/>
-      <c r="G46" s="105">
-        <f>SUM(C46:F46)</f>
-        <v/>
-      </c>
-      <c r="H46" s="105">
-        <f>B46+G46</f>
+      <c r="D46" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="101" t="n"/>
+      <c r="G46" s="101">
+        <f>C46+D46+E46+F46</f>
+        <v/>
+      </c>
+      <c r="H46" s="101">
+        <f>G46+B46</f>
         <v/>
       </c>
       <c r="I46" s="113">
         <f>IFERROR(LOOKUP(2,1/((B46&lt;$J$3:$R$3)*(H46&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J46" s="105" t="n"/>
-      <c r="K46" s="105" t="n"/>
-      <c r="L46" s="105" t="n"/>
-      <c r="M46" s="105" t="n"/>
-      <c r="N46" s="105" t="n"/>
-      <c r="O46" s="105" t="n"/>
-      <c r="P46" s="105" t="n"/>
-      <c r="Q46" s="105" t="n"/>
-      <c r="R46" s="105" t="n"/>
-    </row>
-    <row r="47" ht="13.2" customHeight="1" s="103">
-      <c r="A47" s="107" t="inlineStr">
+      <c r="J46" s="101" t="n"/>
+      <c r="K46" s="101" t="n"/>
+      <c r="L46" s="101" t="n"/>
+      <c r="M46" s="101" t="n"/>
+      <c r="N46" s="101" t="n"/>
+      <c r="O46" s="101" t="n"/>
+      <c r="P46" s="101" t="n"/>
+      <c r="Q46" s="101" t="n"/>
+      <c r="R46" s="101" t="n"/>
+    </row>
+    <row r="47" ht="13.15" customHeight="1" s="91">
+      <c r="A47" s="103" t="inlineStr">
         <is>
           <t>Pfundstein, Andreas</t>
         </is>
       </c>
-      <c r="B47" s="108">
-        <f>'24-25'!H44</f>
-        <v/>
-      </c>
-      <c r="C47" s="108" t="n">
+      <c r="B47" s="104">
+        <f>'24-25'!H45</f>
+        <v/>
+      </c>
+      <c r="C47" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="D47" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="108" t="n"/>
-      <c r="G47" s="108">
-        <f>SUM(C47:F47)</f>
-        <v/>
-      </c>
-      <c r="H47" s="108">
-        <f>B47+G47</f>
-        <v/>
-      </c>
-      <c r="I47" s="112">
+      <c r="D47" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="104" t="n"/>
+      <c r="G47" s="104">
+        <f>C47+D47+E47+F47</f>
+        <v/>
+      </c>
+      <c r="H47" s="104">
+        <f>G47+B47</f>
+        <v/>
+      </c>
+      <c r="I47" s="114">
         <f>IFERROR(LOOKUP(2,1/((B47&lt;$J$3:$R$3)*(H47&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J47" s="108" t="n"/>
-      <c r="K47" s="108" t="n"/>
-      <c r="L47" s="108" t="n"/>
-      <c r="M47" s="108" t="n"/>
-      <c r="N47" s="108" t="n"/>
-      <c r="O47" s="108" t="n"/>
-      <c r="P47" s="108" t="n"/>
-      <c r="Q47" s="108" t="n"/>
-      <c r="R47" s="108" t="n"/>
-    </row>
-    <row r="48" ht="13.2" customHeight="1" s="103">
-      <c r="A48" s="104" t="inlineStr">
+      <c r="J47" s="104" t="n"/>
+      <c r="K47" s="104" t="n"/>
+      <c r="L47" s="104" t="n"/>
+      <c r="M47" s="104" t="n"/>
+      <c r="N47" s="104" t="n"/>
+      <c r="O47" s="104" t="n"/>
+      <c r="P47" s="104" t="n"/>
+      <c r="Q47" s="104" t="n"/>
+      <c r="R47" s="104" t="n"/>
+    </row>
+    <row r="48" ht="13.15" customHeight="1" s="91">
+      <c r="A48" s="100" t="inlineStr">
         <is>
           <t>Preuss, Jonas</t>
         </is>
       </c>
-      <c r="B48" s="105">
-        <f>'24-25'!H45</f>
-        <v/>
-      </c>
-      <c r="C48" s="105" t="n">
+      <c r="B48" s="101">
+        <f>'24-25'!H46</f>
+        <v/>
+      </c>
+      <c r="C48" s="101" t="n">
         <v>9</v>
       </c>
-      <c r="D48" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="105" t="n">
+      <c r="D48" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="101" t="n">
         <v>6</v>
       </c>
-      <c r="F48" s="105" t="n"/>
-      <c r="G48" s="105">
-        <f>SUM(C48:F48)</f>
-        <v/>
-      </c>
-      <c r="H48" s="105">
-        <f>B48+G48</f>
+      <c r="F48" s="101" t="n"/>
+      <c r="G48" s="101">
+        <f>C48+D48+E48+F48</f>
+        <v/>
+      </c>
+      <c r="H48" s="101">
+        <f>G48+B48</f>
         <v/>
       </c>
       <c r="I48" s="113">
         <f>IFERROR(LOOKUP(2,1/((B48&lt;$J$3:$R$3)*(H48&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J48" s="105" t="n"/>
-      <c r="K48" s="105" t="n"/>
-      <c r="L48" s="105" t="n"/>
-      <c r="M48" s="105" t="n"/>
-      <c r="N48" s="105" t="n"/>
-      <c r="O48" s="105" t="n"/>
-      <c r="P48" s="105" t="n"/>
-      <c r="Q48" s="105" t="n"/>
-      <c r="R48" s="105" t="n"/>
-    </row>
-    <row r="49" ht="13.2" customHeight="1" s="103">
-      <c r="A49" s="107" t="inlineStr">
+      <c r="J48" s="101" t="n"/>
+      <c r="K48" s="101" t="n"/>
+      <c r="L48" s="101" t="n"/>
+      <c r="M48" s="101" t="n"/>
+      <c r="N48" s="101" t="n"/>
+      <c r="O48" s="101" t="n"/>
+      <c r="P48" s="101" t="n"/>
+      <c r="Q48" s="101" t="n"/>
+      <c r="R48" s="101" t="n"/>
+    </row>
+    <row r="49" ht="13.15" customHeight="1" s="91">
+      <c r="A49" s="103" t="inlineStr">
         <is>
           <t>Rieder, Sebastian</t>
         </is>
       </c>
-      <c r="B49" s="110">
+      <c r="B49" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C49" s="108" t="n">
+      <c r="C49" s="104" t="n">
         <v>18</v>
       </c>
-      <c r="D49" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="108" t="n">
+      <c r="D49" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="104" t="n">
         <v>6</v>
       </c>
-      <c r="F49" s="108" t="n"/>
-      <c r="G49" s="108">
-        <f>SUM(C49:F49)</f>
-        <v/>
-      </c>
-      <c r="H49" s="108">
-        <f>B49+G49</f>
-        <v/>
-      </c>
-      <c r="I49" s="109">
+      <c r="F49" s="104" t="n"/>
+      <c r="G49" s="104">
+        <f>C49+D49+E49+F49</f>
+        <v/>
+      </c>
+      <c r="H49" s="104">
+        <f>G49+B49</f>
+        <v/>
+      </c>
+      <c r="I49" s="114">
         <f>IFERROR(LOOKUP(2,1/((B49&lt;$J$3:$R$3)*(H49&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J49" s="108" t="n"/>
-      <c r="K49" s="108" t="n"/>
-      <c r="L49" s="108" t="n"/>
-      <c r="M49" s="108" t="n"/>
-      <c r="N49" s="108" t="n"/>
-      <c r="O49" s="108" t="n"/>
-      <c r="P49" s="108" t="n"/>
-      <c r="Q49" s="108" t="n"/>
-      <c r="R49" s="108" t="n"/>
-    </row>
-    <row r="50" ht="13.2" customHeight="1" s="103">
-      <c r="A50" s="104" t="inlineStr">
+      <c r="J49" s="104" t="n"/>
+      <c r="K49" s="104" t="n"/>
+      <c r="L49" s="104" t="n"/>
+      <c r="M49" s="104" t="n"/>
+      <c r="N49" s="104" t="n"/>
+      <c r="O49" s="104" t="n"/>
+      <c r="P49" s="104" t="n"/>
+      <c r="Q49" s="104" t="n"/>
+      <c r="R49" s="104" t="n"/>
+    </row>
+    <row r="50" ht="13.15" customHeight="1" s="91">
+      <c r="A50" s="100" t="inlineStr">
         <is>
           <t>Sauter, Alexander</t>
         </is>
       </c>
-      <c r="B50" s="111">
+      <c r="B50" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C50" s="105" t="n">
+      <c r="C50" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="105" t="n"/>
-      <c r="G50" s="105">
-        <f>SUM(C50:F50)</f>
-        <v/>
-      </c>
-      <c r="H50" s="105">
-        <f>B50+G50</f>
-        <v/>
-      </c>
-      <c r="I50" s="106">
+      <c r="D50" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="101" t="n"/>
+      <c r="G50" s="101">
+        <f>C50+D50+E50+F50</f>
+        <v/>
+      </c>
+      <c r="H50" s="101">
+        <f>G50+B50</f>
+        <v/>
+      </c>
+      <c r="I50" s="113">
         <f>IFERROR(LOOKUP(2,1/((B50&lt;$J$3:$R$3)*(H50&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J50" s="105" t="n"/>
-      <c r="K50" s="105" t="n"/>
-      <c r="L50" s="105" t="n"/>
-      <c r="M50" s="105" t="n"/>
-      <c r="N50" s="105" t="n"/>
-      <c r="O50" s="105" t="n"/>
-      <c r="P50" s="105" t="n"/>
-      <c r="Q50" s="105" t="n"/>
-      <c r="R50" s="105" t="n"/>
-    </row>
-    <row r="51" ht="13.2" customHeight="1" s="103">
-      <c r="A51" s="107" t="inlineStr">
+      <c r="J50" s="101" t="n"/>
+      <c r="K50" s="101" t="n"/>
+      <c r="L50" s="101" t="n"/>
+      <c r="M50" s="101" t="n"/>
+      <c r="N50" s="101" t="n"/>
+      <c r="O50" s="101" t="n"/>
+      <c r="P50" s="101" t="n"/>
+      <c r="Q50" s="101" t="n"/>
+      <c r="R50" s="101" t="n"/>
+    </row>
+    <row r="51" ht="13.15" customHeight="1" s="91">
+      <c r="A51" s="103" t="inlineStr">
         <is>
           <t>Sauter, Marius</t>
         </is>
       </c>
-      <c r="B51" s="110">
+      <c r="B51" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C51" s="108" t="n">
+      <c r="C51" s="104" t="n">
         <v>14</v>
       </c>
-      <c r="D51" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="108" t="n">
+      <c r="D51" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="F51" s="108" t="n"/>
-      <c r="G51" s="108">
-        <f>SUM(C51:F51)</f>
-        <v/>
-      </c>
-      <c r="H51" s="108">
-        <f>B51+G51</f>
-        <v/>
-      </c>
-      <c r="I51" s="109">
+      <c r="F51" s="104" t="n"/>
+      <c r="G51" s="104">
+        <f>C51+D51+E51+F51</f>
+        <v/>
+      </c>
+      <c r="H51" s="104">
+        <f>G51+B51</f>
+        <v/>
+      </c>
+      <c r="I51" s="114">
         <f>IFERROR(LOOKUP(2,1/((B51&lt;$J$3:$R$3)*(H51&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J51" s="108" t="n"/>
-      <c r="K51" s="108" t="n"/>
-      <c r="L51" s="108" t="n"/>
-      <c r="M51" s="108" t="n"/>
-      <c r="N51" s="108" t="n"/>
-      <c r="O51" s="108" t="n"/>
-      <c r="P51" s="108" t="n"/>
-      <c r="Q51" s="108" t="n"/>
-      <c r="R51" s="108" t="n"/>
-    </row>
-    <row r="52" ht="13.2" customHeight="1" s="103">
-      <c r="A52" s="104" t="inlineStr">
+      <c r="J51" s="104" t="n"/>
+      <c r="K51" s="104" t="n"/>
+      <c r="L51" s="104" t="n"/>
+      <c r="M51" s="104" t="n"/>
+      <c r="N51" s="104" t="n"/>
+      <c r="O51" s="104" t="n"/>
+      <c r="P51" s="104" t="n"/>
+      <c r="Q51" s="104" t="n"/>
+      <c r="R51" s="104" t="n"/>
+    </row>
+    <row r="52" ht="13.15" customHeight="1" s="91">
+      <c r="A52" s="100" t="inlineStr">
         <is>
           <t>Schaumann, Daniel</t>
         </is>
       </c>
-      <c r="B52" s="105">
-        <f>'24-25'!H47</f>
-        <v/>
-      </c>
-      <c r="C52" s="105" t="n">
+      <c r="B52" s="101">
+        <f>'24-25'!H48</f>
+        <v/>
+      </c>
+      <c r="C52" s="101" t="n">
         <v>22</v>
       </c>
-      <c r="D52" s="105" t="n">
+      <c r="D52" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="E52" s="105" t="n">
+      <c r="E52" s="101" t="n">
         <v>6</v>
       </c>
-      <c r="F52" s="105" t="n"/>
-      <c r="G52" s="105">
-        <f>SUM(C52:F52)</f>
-        <v/>
-      </c>
-      <c r="H52" s="105">
-        <f>B52+G52</f>
-        <v/>
-      </c>
-      <c r="I52" s="106">
+      <c r="F52" s="101" t="n"/>
+      <c r="G52" s="101">
+        <f>C52+D52+E52+F52</f>
+        <v/>
+      </c>
+      <c r="H52" s="101">
+        <f>G52+B52</f>
+        <v/>
+      </c>
+      <c r="I52" s="113">
         <f>IFERROR(LOOKUP(2,1/((B52&lt;$J$3:$R$3)*(H52&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J52" s="105" t="n"/>
-      <c r="K52" s="105" t="n"/>
-      <c r="L52" s="105" t="n"/>
-      <c r="M52" s="105" t="n"/>
-      <c r="N52" s="105" t="n"/>
-      <c r="O52" s="105" t="n"/>
-      <c r="P52" s="105" t="n"/>
-      <c r="Q52" s="105" t="n"/>
-      <c r="R52" s="105" t="n"/>
-    </row>
-    <row r="53" ht="13.2" customHeight="1" s="103">
-      <c r="A53" s="107" t="inlineStr">
+      <c r="J52" s="101" t="n"/>
+      <c r="K52" s="101" t="n"/>
+      <c r="L52" s="101" t="n"/>
+      <c r="M52" s="101" t="n"/>
+      <c r="N52" s="101" t="n"/>
+      <c r="O52" s="101" t="n"/>
+      <c r="P52" s="101" t="n"/>
+      <c r="Q52" s="101" t="n"/>
+      <c r="R52" s="101" t="n"/>
+    </row>
+    <row r="53" ht="13.15" customHeight="1" s="91">
+      <c r="A53" s="103" t="inlineStr">
         <is>
           <t>Schaumann, David</t>
         </is>
       </c>
-      <c r="B53" s="108">
-        <f>'24-25'!H48</f>
-        <v/>
-      </c>
-      <c r="C53" s="108" t="n">
+      <c r="B53" s="104">
+        <f>'24-25'!H49</f>
+        <v/>
+      </c>
+      <c r="C53" s="104" t="n">
         <v>19</v>
       </c>
-      <c r="D53" s="108" t="n">
+      <c r="D53" s="104" t="n">
         <v>2</v>
       </c>
-      <c r="E53" s="108" t="n">
+      <c r="E53" s="104" t="n">
         <v>8</v>
       </c>
-      <c r="F53" s="108" t="n"/>
-      <c r="G53" s="108">
-        <f>SUM(C53:F53)</f>
-        <v/>
-      </c>
-      <c r="H53" s="108">
-        <f>B53+G53</f>
-        <v/>
-      </c>
-      <c r="I53" s="109">
+      <c r="F53" s="104" t="n"/>
+      <c r="G53" s="104">
+        <f>C53+D53+E53+F53</f>
+        <v/>
+      </c>
+      <c r="H53" s="104">
+        <f>G53+B53</f>
+        <v/>
+      </c>
+      <c r="I53" s="114">
         <f>IFERROR(LOOKUP(2,1/((B53&lt;$J$3:$R$3)*(H53&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J53" s="108" t="n"/>
-      <c r="K53" s="108" t="n"/>
-      <c r="L53" s="108" t="n"/>
-      <c r="M53" s="108" t="n"/>
-      <c r="N53" s="108" t="n"/>
-      <c r="O53" s="108" t="n"/>
-      <c r="P53" s="108" t="n"/>
-      <c r="Q53" s="108" t="n"/>
-      <c r="R53" s="108" t="n"/>
-    </row>
-    <row r="54" ht="13.2" customHeight="1" s="103">
-      <c r="A54" s="104" t="inlineStr">
+      <c r="J53" s="104" t="n"/>
+      <c r="K53" s="104" t="n"/>
+      <c r="L53" s="104" t="n"/>
+      <c r="M53" s="104" t="n"/>
+      <c r="N53" s="104" t="n"/>
+      <c r="O53" s="104" t="n"/>
+      <c r="P53" s="104" t="n"/>
+      <c r="Q53" s="104" t="n"/>
+      <c r="R53" s="104" t="n"/>
+    </row>
+    <row r="54" ht="13.15" customHeight="1" s="91">
+      <c r="A54" s="100" t="inlineStr">
         <is>
           <t>Schaumann, Sebastian</t>
         </is>
       </c>
-      <c r="B54" s="105">
-        <f>'24-25'!H49</f>
-        <v/>
-      </c>
-      <c r="C54" s="105" t="n">
+      <c r="B54" s="101">
+        <f>'24-25'!H50</f>
+        <v/>
+      </c>
+      <c r="C54" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="D54" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="105" t="n">
+      <c r="D54" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="101" t="n">
         <v>4</v>
       </c>
-      <c r="F54" s="105" t="n"/>
-      <c r="G54" s="105">
-        <f>SUM(C54:F54)</f>
-        <v/>
-      </c>
-      <c r="H54" s="105">
-        <f>B54+G54</f>
-        <v/>
-      </c>
-      <c r="I54" s="106">
+      <c r="F54" s="101" t="n"/>
+      <c r="G54" s="101">
+        <f>C54+D54+E54+F54</f>
+        <v/>
+      </c>
+      <c r="H54" s="101">
+        <f>G54+B54</f>
+        <v/>
+      </c>
+      <c r="I54" s="113">
         <f>IFERROR(LOOKUP(2,1/((B54&lt;$J$3:$R$3)*(H54&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J54" s="105" t="n"/>
-      <c r="K54" s="105" t="n"/>
-      <c r="L54" s="105" t="n"/>
-      <c r="M54" s="105" t="n"/>
-      <c r="N54" s="105" t="n"/>
-      <c r="O54" s="105" t="n"/>
-      <c r="P54" s="105" t="n"/>
-      <c r="Q54" s="105" t="n"/>
-      <c r="R54" s="105" t="n"/>
-    </row>
-    <row r="55" ht="13.2" customHeight="1" s="103">
-      <c r="A55" s="107" t="inlineStr">
+      <c r="J54" s="101" t="n"/>
+      <c r="K54" s="101" t="n"/>
+      <c r="L54" s="101" t="n"/>
+      <c r="M54" s="101" t="n"/>
+      <c r="N54" s="101" t="n"/>
+      <c r="O54" s="101" t="n"/>
+      <c r="P54" s="101" t="n"/>
+      <c r="Q54" s="101" t="n"/>
+      <c r="R54" s="101" t="n"/>
+    </row>
+    <row r="55" ht="13.15" customHeight="1" s="91">
+      <c r="A55" s="103" t="inlineStr">
         <is>
           <t>Schmidt, Nicolas</t>
         </is>
       </c>
-      <c r="B55" s="110">
+      <c r="B55" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C55" s="108" t="n">
+      <c r="C55" s="104" t="n">
         <v>7</v>
       </c>
-      <c r="D55" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="108" t="n">
+      <c r="D55" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="104" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="108" t="n"/>
-      <c r="G55" s="108">
-        <f>SUM(C55:F55)</f>
-        <v/>
-      </c>
-      <c r="H55" s="108">
-        <f>B55+G55</f>
-        <v/>
-      </c>
-      <c r="I55" s="109">
+      <c r="F55" s="104" t="n"/>
+      <c r="G55" s="104">
+        <f>C55+D55+E55+F55</f>
+        <v/>
+      </c>
+      <c r="H55" s="104">
+        <f>G55+B55</f>
+        <v/>
+      </c>
+      <c r="I55" s="114">
         <f>IFERROR(LOOKUP(2,1/((B55&lt;$J$3:$R$3)*(H55&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J55" s="108" t="n"/>
-      <c r="K55" s="108" t="n"/>
-      <c r="L55" s="108" t="n"/>
-      <c r="M55" s="108" t="n"/>
-      <c r="N55" s="108" t="n"/>
-      <c r="O55" s="108" t="n"/>
-      <c r="P55" s="108" t="n"/>
-      <c r="Q55" s="108" t="n"/>
-      <c r="R55" s="108" t="n"/>
-    </row>
-    <row r="56" ht="13.2" customHeight="1" s="103">
-      <c r="A56" s="104" t="inlineStr">
+      <c r="J55" s="104" t="n"/>
+      <c r="K55" s="104" t="n"/>
+      <c r="L55" s="104" t="n"/>
+      <c r="M55" s="104" t="n"/>
+      <c r="N55" s="104" t="n"/>
+      <c r="O55" s="104" t="n"/>
+      <c r="P55" s="104" t="n"/>
+      <c r="Q55" s="104" t="n"/>
+      <c r="R55" s="104" t="n"/>
+    </row>
+    <row r="56" ht="13.15" customHeight="1" s="91">
+      <c r="A56" s="100" t="inlineStr">
         <is>
           <t>Staiger, Simon</t>
         </is>
       </c>
-      <c r="B56" s="111">
+      <c r="B56" s="106">
         <f>0</f>
         <v/>
       </c>
-      <c r="C56" s="105" t="n">
+      <c r="C56" s="101" t="n">
         <v>16</v>
       </c>
-      <c r="D56" s="105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="105" t="n">
+      <c r="D56" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="F56" s="105" t="n"/>
-      <c r="G56" s="105">
-        <f>SUM(C56:F56)</f>
-        <v/>
-      </c>
-      <c r="H56" s="105">
-        <f>B56+G56</f>
-        <v/>
-      </c>
-      <c r="I56" s="106">
+      <c r="F56" s="101" t="n"/>
+      <c r="G56" s="101">
+        <f>C56+D56+E56+F56</f>
+        <v/>
+      </c>
+      <c r="H56" s="101">
+        <f>G56+B56</f>
+        <v/>
+      </c>
+      <c r="I56" s="113">
         <f>IFERROR(LOOKUP(2,1/((B56&lt;$J$3:$R$3)*(H56&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J56" s="105" t="n"/>
-      <c r="K56" s="105" t="n"/>
-      <c r="L56" s="105" t="n"/>
-      <c r="M56" s="105" t="n"/>
-      <c r="N56" s="105" t="n"/>
-      <c r="O56" s="105" t="n"/>
-      <c r="P56" s="105" t="n"/>
-      <c r="Q56" s="105" t="n"/>
-      <c r="R56" s="105" t="n"/>
-    </row>
-    <row r="57" ht="13.2" customHeight="1" s="103">
-      <c r="A57" s="107" t="inlineStr">
+      <c r="J56" s="101" t="n"/>
+      <c r="K56" s="101" t="n"/>
+      <c r="L56" s="101" t="n"/>
+      <c r="M56" s="101" t="n"/>
+      <c r="N56" s="101" t="n"/>
+      <c r="O56" s="101" t="n"/>
+      <c r="P56" s="101" t="n"/>
+      <c r="Q56" s="101" t="n"/>
+      <c r="R56" s="101" t="n"/>
+    </row>
+    <row r="57" ht="13.15" customHeight="1" s="91">
+      <c r="A57" s="103" t="inlineStr">
         <is>
           <t>Staiger, Tobias</t>
         </is>
       </c>
-      <c r="B57" s="108">
-        <f>'24-25'!H53</f>
-        <v/>
-      </c>
-      <c r="C57" s="108" t="n">
+      <c r="B57" s="104">
+        <f>'24-25'!H54</f>
+        <v/>
+      </c>
+      <c r="C57" s="104" t="n">
         <v>11</v>
       </c>
-      <c r="D57" s="108" t="n">
+      <c r="D57" s="104" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="108" t="n">
+      <c r="E57" s="104" t="n">
         <v>9</v>
       </c>
-      <c r="F57" s="108" t="n"/>
-      <c r="G57" s="108">
-        <f>SUM(C57:F57)</f>
-        <v/>
-      </c>
-      <c r="H57" s="108">
-        <f>B57+G57</f>
-        <v/>
-      </c>
-      <c r="I57" s="109">
+      <c r="F57" s="104" t="n"/>
+      <c r="G57" s="104">
+        <f>C57+D57+E57+F57</f>
+        <v/>
+      </c>
+      <c r="H57" s="104">
+        <f>G57+B57</f>
+        <v/>
+      </c>
+      <c r="I57" s="114">
         <f>IFERROR(LOOKUP(2,1/((B57&lt;$J$3:$R$3)*(H57&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J57" s="108" t="n"/>
-      <c r="K57" s="108" t="n"/>
-      <c r="L57" s="108" t="n"/>
-      <c r="M57" s="108" t="n"/>
-      <c r="N57" s="108" t="n"/>
-      <c r="O57" s="108" t="n"/>
-      <c r="P57" s="108" t="n"/>
-      <c r="Q57" s="108" t="n"/>
-      <c r="R57" s="108" t="n"/>
-    </row>
-    <row r="58" ht="13.2" customHeight="1" s="103">
-      <c r="A58" s="105" t="inlineStr">
+      <c r="J57" s="104" t="n"/>
+      <c r="K57" s="104" t="n"/>
+      <c r="L57" s="104" t="n"/>
+      <c r="M57" s="104" t="n"/>
+      <c r="N57" s="104" t="n"/>
+      <c r="O57" s="104" t="n"/>
+      <c r="P57" s="104" t="n"/>
+      <c r="Q57" s="104" t="n"/>
+      <c r="R57" s="104" t="n"/>
+    </row>
+    <row r="58" ht="13.15" customHeight="1" s="91">
+      <c r="A58" s="100" t="inlineStr">
         <is>
           <t>Tramnitz, Lukas</t>
         </is>
       </c>
-      <c r="B58" s="105">
-        <f>'24-25'!H55</f>
-        <v/>
-      </c>
-      <c r="C58" s="105" t="n">
+      <c r="B58" s="101">
+        <f>'24-25'!H56</f>
+        <v/>
+      </c>
+      <c r="C58" s="101" t="n">
         <v>21</v>
       </c>
-      <c r="D58" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="105" t="n">
+      <c r="D58" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="F58" s="105" t="n"/>
-      <c r="G58" s="105">
-        <f>SUM(C58:F58)</f>
-        <v/>
-      </c>
-      <c r="H58" s="105">
-        <f>B58+G58</f>
-        <v/>
-      </c>
-      <c r="I58" s="105">
+      <c r="F58" s="101" t="n"/>
+      <c r="G58" s="101">
+        <f>C58+D58+E58+F58</f>
+        <v/>
+      </c>
+      <c r="H58" s="101">
+        <f>G58+B58</f>
+        <v/>
+      </c>
+      <c r="I58" s="113">
         <f>IFERROR(LOOKUP(2,1/((B58&lt;$J$3:$R$3)*(H58&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J58" s="105" t="n"/>
-      <c r="K58" s="105" t="n"/>
-      <c r="L58" s="105" t="n"/>
-      <c r="M58" s="105" t="n"/>
-      <c r="N58" s="105" t="n"/>
-      <c r="O58" s="105" t="n"/>
-      <c r="P58" s="105" t="n"/>
-      <c r="Q58" s="105" t="n"/>
-      <c r="R58" s="105" t="n"/>
-    </row>
-    <row r="59" ht="13.2" customHeight="1" s="103">
-      <c r="A59" s="108" t="inlineStr">
+      <c r="J58" s="101" t="n"/>
+      <c r="K58" s="101" t="n"/>
+      <c r="L58" s="101" t="n"/>
+      <c r="M58" s="101" t="n"/>
+      <c r="N58" s="101" t="n"/>
+      <c r="O58" s="101" t="n"/>
+      <c r="P58" s="101" t="n"/>
+      <c r="Q58" s="101" t="n"/>
+      <c r="R58" s="101" t="n"/>
+    </row>
+    <row r="59" ht="13.15" customHeight="1" s="91">
+      <c r="A59" s="104" t="inlineStr">
         <is>
           <t>Verrino, Roberto</t>
         </is>
       </c>
-      <c r="B59" s="108">
-        <f>'24-25'!H56</f>
-        <v/>
-      </c>
-      <c r="C59" s="108" t="n">
+      <c r="B59" s="104">
+        <f>'24-25'!H57</f>
+        <v/>
+      </c>
+      <c r="C59" s="104" t="n">
         <v>18</v>
       </c>
-      <c r="D59" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="108" t="n">
+      <c r="D59" s="104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="104" t="n">
         <v>7</v>
       </c>
-      <c r="F59" s="108" t="n"/>
-      <c r="G59" s="108">
-        <f>SUM(C59:F59)</f>
-        <v/>
-      </c>
-      <c r="H59" s="108">
-        <f>B59+G59</f>
-        <v/>
-      </c>
-      <c r="I59" s="108">
+      <c r="F59" s="104" t="n"/>
+      <c r="G59" s="104">
+        <f>C59+D59+E59+F59</f>
+        <v/>
+      </c>
+      <c r="H59" s="104">
+        <f>G59+B59</f>
+        <v/>
+      </c>
+      <c r="I59" s="107">
         <f>IFERROR(LOOKUP(2,1/((B59&lt;$J$3:$R$3)*(H59&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J59" s="108" t="n"/>
-      <c r="K59" s="108" t="n"/>
-      <c r="L59" s="108" t="n"/>
-      <c r="M59" s="108" t="n"/>
-      <c r="N59" s="108" t="n"/>
-      <c r="O59" s="108" t="n"/>
-      <c r="P59" s="108" t="n"/>
-      <c r="Q59" s="108" t="n"/>
-      <c r="R59" s="108" t="n"/>
-    </row>
-    <row r="60" ht="13.2" customHeight="1" s="103">
-      <c r="A60" s="105" t="inlineStr">
+      <c r="J59" s="104" t="n"/>
+      <c r="K59" s="104" t="n"/>
+      <c r="L59" s="104" t="n"/>
+      <c r="M59" s="104" t="n"/>
+      <c r="N59" s="104" t="n"/>
+      <c r="O59" s="104" t="n"/>
+      <c r="P59" s="104" t="n"/>
+      <c r="Q59" s="104" t="n"/>
+      <c r="R59" s="104" t="n"/>
+    </row>
+    <row r="60" ht="13.15" customHeight="1" s="91">
+      <c r="A60" s="101" t="inlineStr">
         <is>
           <t>Weber, Peter</t>
         </is>
       </c>
-      <c r="B60" s="105">
-        <f>'24-25'!H57</f>
-        <v/>
-      </c>
-      <c r="C60" s="105" t="n">
+      <c r="B60" s="101">
+        <f>'24-25'!H58</f>
+        <v/>
+      </c>
+      <c r="C60" s="101" t="n">
         <v>22</v>
       </c>
-      <c r="D60" s="105" t="n">
+      <c r="D60" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="105" t="n">
+      <c r="E60" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="F60" s="105" t="n"/>
-      <c r="G60" s="105">
-        <f>SUM(C60:F60)</f>
-        <v/>
-      </c>
-      <c r="H60" s="105">
-        <f>B60+G60</f>
-        <v/>
-      </c>
-      <c r="I60" s="105">
+      <c r="F60" s="101" t="n"/>
+      <c r="G60" s="101">
+        <f>C60+D60+E60+F60</f>
+        <v/>
+      </c>
+      <c r="H60" s="101">
+        <f>G60+B60</f>
+        <v/>
+      </c>
+      <c r="I60" s="106">
         <f>IFERROR(LOOKUP(2,1/((B60&lt;$J$3:$R$3)*(H60&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J60" s="105" t="n"/>
-      <c r="K60" s="105" t="n"/>
-      <c r="L60" s="105" t="n"/>
-      <c r="M60" s="105" t="n"/>
-      <c r="N60" s="105" t="n"/>
-      <c r="O60" s="105" t="n"/>
-      <c r="P60" s="105" t="n"/>
-      <c r="Q60" s="105" t="n"/>
-      <c r="R60" s="105" t="n"/>
-    </row>
-    <row r="61" ht="13.2" customHeight="1" s="103">
-      <c r="A61" s="108" t="inlineStr">
+      <c r="J60" s="101" t="n"/>
+      <c r="K60" s="101" t="n"/>
+      <c r="L60" s="101" t="n"/>
+      <c r="M60" s="101" t="n"/>
+      <c r="N60" s="101" t="n"/>
+      <c r="O60" s="101" t="n"/>
+      <c r="P60" s="101" t="n"/>
+      <c r="Q60" s="101" t="n"/>
+      <c r="R60" s="101" t="n"/>
+    </row>
+    <row r="61" ht="13.15" customHeight="1" s="91">
+      <c r="A61" s="104" t="inlineStr">
         <is>
           <t>Wetzel, Maxim</t>
         </is>
       </c>
-      <c r="B61" s="110">
+      <c r="B61" s="107">
         <f>0</f>
         <v/>
       </c>
-      <c r="C61" s="108" t="n">
+      <c r="C61" s="104" t="n">
         <v>18</v>
       </c>
-      <c r="D61" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="108" t="n">
+      <c r="D61" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="104" t="n">
         <v>5</v>
       </c>
-      <c r="F61" s="108" t="n"/>
-      <c r="G61" s="108">
-        <f>SUM(C61:F61)</f>
-        <v/>
-      </c>
-      <c r="H61" s="108">
-        <f>B61+G61</f>
-        <v/>
-      </c>
-      <c r="I61" s="108">
+      <c r="F61" s="104" t="n"/>
+      <c r="G61" s="104">
+        <f>C61+D61+E61+F61</f>
+        <v/>
+      </c>
+      <c r="H61" s="104">
+        <f>G61+B61</f>
+        <v/>
+      </c>
+      <c r="I61" s="107">
         <f>IFERROR(LOOKUP(2,1/((B61&lt;$J$3:$R$3)*(H61&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
-      <c r="J61" s="108" t="n"/>
-      <c r="K61" s="108" t="n"/>
-      <c r="L61" s="108" t="n"/>
-      <c r="M61" s="108" t="n"/>
-      <c r="N61" s="108" t="n"/>
-      <c r="O61" s="108" t="n"/>
-      <c r="P61" s="108" t="n"/>
-      <c r="Q61" s="108" t="n"/>
-      <c r="R61" s="108" t="n"/>
-    </row>
-    <row r="62" ht="13.2" customHeight="1" s="103">
-      <c r="A62" s="105" t="n"/>
-      <c r="B62" s="114" t="n"/>
-      <c r="C62" s="105" t="n"/>
-      <c r="D62" s="105" t="n"/>
-      <c r="E62" s="105" t="n"/>
-      <c r="F62" s="115" t="n"/>
-      <c r="G62" s="105" t="n"/>
-      <c r="H62" s="105" t="n"/>
-      <c r="I62" s="105" t="n"/>
-      <c r="J62" s="105" t="n"/>
-      <c r="K62" s="105" t="n"/>
-      <c r="L62" s="105" t="n"/>
-      <c r="M62" s="105" t="n"/>
-      <c r="N62" s="105" t="n"/>
-      <c r="O62" s="105" t="n"/>
-      <c r="P62" s="105" t="n"/>
-      <c r="Q62" s="105" t="n"/>
-      <c r="R62" s="105" t="n"/>
-    </row>
-    <row r="63" ht="13.2" customHeight="1" s="103">
-      <c r="A63" s="108" t="n"/>
-      <c r="B63" s="108" t="n"/>
-      <c r="C63" s="108" t="n"/>
-      <c r="D63" s="108" t="n"/>
-      <c r="E63" s="108" t="n"/>
-      <c r="F63" s="108" t="n"/>
-      <c r="G63" s="108" t="n"/>
-      <c r="H63" s="108" t="n"/>
-      <c r="I63" s="108" t="n"/>
-      <c r="J63" s="108" t="n"/>
-      <c r="K63" s="108" t="n"/>
-      <c r="L63" s="108" t="n"/>
-      <c r="M63" s="108" t="n"/>
-      <c r="N63" s="108" t="n"/>
-      <c r="O63" s="108" t="n"/>
-      <c r="P63" s="108" t="n"/>
-      <c r="Q63" s="108" t="n"/>
-      <c r="R63" s="108" t="n"/>
-    </row>
-    <row r="64" ht="12.75" customHeight="1" s="103">
-      <c r="A64" s="105" t="n"/>
-      <c r="B64" s="116" t="n"/>
-      <c r="C64" s="105" t="n"/>
-      <c r="D64" s="105" t="n"/>
-      <c r="E64" s="105" t="n"/>
-      <c r="F64" s="105" t="n"/>
-      <c r="G64" s="105" t="n"/>
-      <c r="H64" s="105" t="n"/>
-      <c r="I64" s="105" t="n"/>
-      <c r="J64" s="105" t="n"/>
-      <c r="K64" s="105" t="n"/>
-      <c r="L64" s="105" t="n"/>
-      <c r="M64" s="105" t="n"/>
-      <c r="N64" s="105" t="n"/>
-      <c r="O64" s="105" t="n"/>
-      <c r="P64" s="105" t="n"/>
-      <c r="Q64" s="105" t="n"/>
-      <c r="R64" s="105" t="n"/>
+      <c r="J61" s="104" t="n"/>
+      <c r="K61" s="104" t="n"/>
+      <c r="L61" s="104" t="n"/>
+      <c r="M61" s="104" t="n"/>
+      <c r="N61" s="104" t="n"/>
+      <c r="O61" s="104" t="n"/>
+      <c r="P61" s="104" t="n"/>
+      <c r="Q61" s="104" t="n"/>
+      <c r="R61" s="104" t="n"/>
+    </row>
+    <row r="62" ht="13.15" customHeight="1" s="91">
+      <c r="A62" s="101" t="n"/>
+      <c r="B62" s="101" t="n"/>
+      <c r="C62" s="101" t="n"/>
+      <c r="D62" s="101" t="n"/>
+      <c r="E62" s="101" t="n"/>
+      <c r="F62" s="101" t="n"/>
+      <c r="G62" s="101" t="n"/>
+      <c r="H62" s="101" t="n"/>
+      <c r="I62" s="106" t="n"/>
+      <c r="J62" s="101" t="n"/>
+      <c r="K62" s="101" t="n"/>
+      <c r="L62" s="101" t="n"/>
+      <c r="M62" s="101" t="n"/>
+      <c r="N62" s="101" t="n"/>
+      <c r="O62" s="101" t="n"/>
+      <c r="P62" s="101" t="n"/>
+      <c r="Q62" s="101" t="n"/>
+      <c r="R62" s="101" t="n"/>
+    </row>
+    <row r="63" ht="13.15" customHeight="1" s="91">
+      <c r="A63" s="104" t="n"/>
+      <c r="B63" s="110" t="n"/>
+      <c r="C63" s="104" t="n"/>
+      <c r="D63" s="104" t="n"/>
+      <c r="E63" s="104" t="n"/>
+      <c r="F63" s="111" t="n"/>
+      <c r="G63" s="104" t="n"/>
+      <c r="H63" s="104" t="n"/>
+      <c r="I63" s="107" t="n"/>
+      <c r="J63" s="104" t="n"/>
+      <c r="K63" s="104" t="n"/>
+      <c r="L63" s="104" t="n"/>
+      <c r="M63" s="104" t="n"/>
+      <c r="N63" s="104" t="n"/>
+      <c r="O63" s="104" t="n"/>
+      <c r="P63" s="104" t="n"/>
+      <c r="Q63" s="104" t="n"/>
+      <c r="R63" s="104" t="n"/>
+    </row>
+    <row r="64" ht="13.15" customHeight="1" s="91">
+      <c r="A64" s="101" t="n"/>
+      <c r="B64" s="101" t="n"/>
+      <c r="C64" s="101" t="n"/>
+      <c r="D64" s="101" t="n"/>
+      <c r="E64" s="101" t="n"/>
+      <c r="F64" s="101" t="n"/>
+      <c r="G64" s="101" t="n"/>
+      <c r="H64" s="101" t="n"/>
+      <c r="I64" s="106" t="n"/>
+      <c r="J64" s="101" t="n"/>
+      <c r="K64" s="101" t="n"/>
+      <c r="L64" s="101" t="n"/>
+      <c r="M64" s="101" t="n"/>
+      <c r="N64" s="101" t="n"/>
+      <c r="O64" s="101" t="n"/>
+      <c r="P64" s="101" t="n"/>
+      <c r="Q64" s="101" t="n"/>
+      <c r="R64" s="101" t="n"/>
+    </row>
+    <row r="65" ht="12.75" customHeight="1" s="91">
+      <c r="A65" s="104" t="n"/>
+      <c r="B65" s="112" t="n"/>
+      <c r="C65" s="104" t="n"/>
+      <c r="D65" s="104" t="n"/>
+      <c r="E65" s="104" t="n"/>
+      <c r="F65" s="104" t="n"/>
+      <c r="G65" s="104" t="n"/>
+      <c r="H65" s="104" t="n"/>
+      <c r="I65" s="107" t="n"/>
+      <c r="J65" s="104" t="n"/>
+      <c r="K65" s="104" t="n"/>
+      <c r="L65" s="104" t="n"/>
+      <c r="M65" s="104" t="n"/>
+      <c r="N65" s="104" t="n"/>
+      <c r="O65" s="104" t="n"/>
+      <c r="P65" s="104" t="n"/>
+      <c r="Q65" s="104" t="n"/>
+      <c r="R65" s="104" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9263,13 +9281,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:CL73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.5546875" bestFit="1" customWidth="1" style="103" min="1" max="1"/>
+    <col width="18.5703125" bestFit="1" customWidth="1" style="91" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.4" customHeight="1" s="103">
-      <c r="E1" s="91" t="inlineStr">
+    <row r="1" ht="35.45" customHeight="1" s="91">
+      <c r="E1" s="90" t="inlineStr">
         <is>
           <t>Saison 13/14</t>
         </is>
@@ -9626,7 +9644,7 @@
       <c r="CH3" s="42" t="n"/>
       <c r="CI3" s="42" t="n"/>
     </row>
-    <row r="4" ht="227.4" customHeight="1" s="103">
+    <row r="4" ht="227.45" customHeight="1" s="91">
       <c r="A4" s="94" t="n"/>
       <c r="B4" s="94" t="n"/>
       <c r="C4" s="97" t="n"/>
@@ -15793,13 +15811,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:CL75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.5546875" bestFit="1" customWidth="1" style="103" min="1" max="1"/>
+    <col width="18.5703125" bestFit="1" customWidth="1" style="91" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.4" customHeight="1" s="103">
-      <c r="E1" s="91" t="inlineStr">
+    <row r="1" ht="35.45" customHeight="1" s="91">
+      <c r="E1" s="90" t="inlineStr">
         <is>
           <t>Saison 14/15</t>
         </is>
@@ -16201,7 +16219,7 @@
       <c r="CH3" s="42" t="n"/>
       <c r="CI3" s="42" t="n"/>
     </row>
-    <row r="4" ht="331.8" customHeight="1" s="103">
+    <row r="4" ht="331.9" customHeight="1" s="91">
       <c r="A4" s="94" t="n"/>
       <c r="B4" s="94" t="n"/>
       <c r="C4" s="97" t="n"/>
@@ -22933,13 +22951,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:CM80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.5546875" bestFit="1" customWidth="1" style="103" min="1" max="1"/>
+    <col width="18.5703125" bestFit="1" customWidth="1" style="91" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.4" customHeight="1" s="103">
-      <c r="E1" s="91" t="inlineStr">
+    <row r="1" ht="35.45" customHeight="1" s="91">
+      <c r="E1" s="90" t="inlineStr">
         <is>
           <t>Saison 15/16</t>
         </is>
@@ -23343,7 +23361,7 @@
       <c r="CI3" s="42" t="n"/>
       <c r="CJ3" s="42" t="n"/>
     </row>
-    <row r="4" ht="355.2" customHeight="1" s="103">
+    <row r="4" ht="355.15" customHeight="1" s="91">
       <c r="A4" s="94" t="n"/>
       <c r="B4" s="94" t="n"/>
       <c r="C4" s="97" t="n"/>
@@ -30657,13 +30675,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:CJ98"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.5546875" bestFit="1" customWidth="1" style="103" min="1" max="1"/>
+    <col width="18.5703125" bestFit="1" customWidth="1" style="91" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.4" customHeight="1" s="103">
-      <c r="E1" s="91" t="inlineStr">
+    <row r="1" ht="35.45" customHeight="1" s="91">
+      <c r="E1" s="90" t="inlineStr">
         <is>
           <t>Saison 17/18</t>
         </is>
@@ -31053,7 +31071,7 @@
       <c r="CF3" s="42" t="n"/>
       <c r="CG3" s="42" t="n"/>
     </row>
-    <row r="4" ht="215.4" customHeight="1" s="103">
+    <row r="4" ht="215.45" customHeight="1" s="91">
       <c r="A4" s="94" t="n"/>
       <c r="B4" s="94" t="n"/>
       <c r="C4" s="97" t="n"/>
@@ -39496,26 +39514,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.44140625" customWidth="1" style="103" min="1" max="1"/>
-    <col width="4.109375" customWidth="1" style="103" min="2" max="2"/>
-    <col width="5.44140625" customWidth="1" style="103" min="3" max="3"/>
-    <col width="10.6640625" customWidth="1" style="103" min="4" max="6"/>
-    <col width="35.44140625" customWidth="1" style="103" min="7" max="7"/>
-    <col width="5.88671875" bestFit="1" customWidth="1" style="103" min="8" max="8"/>
-    <col width="5.88671875" customWidth="1" style="103" min="9" max="9"/>
-    <col width="5.44140625" bestFit="1" customWidth="1" style="103" min="10" max="10"/>
+    <col width="18.42578125" customWidth="1" style="91" min="1" max="1"/>
+    <col width="4.140625" customWidth="1" style="91" min="2" max="2"/>
+    <col width="5.42578125" customWidth="1" style="91" min="3" max="3"/>
+    <col width="10.7109375" customWidth="1" style="91" min="4" max="6"/>
+    <col width="35.42578125" customWidth="1" style="91" min="7" max="7"/>
+    <col width="5.85546875" bestFit="1" customWidth="1" style="91" min="8" max="8"/>
+    <col width="5.85546875" customWidth="1" style="91" min="9" max="9"/>
+    <col width="5.42578125" bestFit="1" customWidth="1" style="91" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.75" customHeight="1" s="103">
+    <row r="1" ht="36.75" customHeight="1" s="91">
       <c r="E1" s="99" t="inlineStr">
         <is>
           <t>Saison 21/22</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="79.5" customHeight="1" s="103">
+    <row r="2" ht="79.5" customHeight="1" s="91">
       <c r="A2" s="8" t="n"/>
       <c r="B2" s="8" t="n"/>
       <c r="C2" s="9" t="n"/>
@@ -39540,7 +39558,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.75" customHeight="1" s="103">
+    <row r="3" ht="12.75" customHeight="1" s="91">
       <c r="A3" s="92" t="inlineStr">
         <is>
           <t>Auber, Manuel</t>
@@ -39563,7 +39581,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="12.75" customHeight="1" s="103">
+    <row r="4" ht="12.75" customHeight="1" s="91">
       <c r="A4" s="92" t="inlineStr">
         <is>
           <t>Aubel, Daniel</t>
@@ -39586,7 +39604,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="12.75" customHeight="1" s="103">
+    <row r="5" ht="12.75" customHeight="1" s="91">
       <c r="A5" s="92" t="inlineStr">
         <is>
           <t>Auber, David</t>
@@ -39609,7 +39627,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="12.75" customHeight="1" s="103">
+    <row r="6" ht="12.75" customHeight="1" s="91">
       <c r="A6" s="92" t="inlineStr">
         <is>
           <t>Bea, Marc</t>
@@ -39632,7 +39650,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="12.75" customHeight="1" s="103">
+    <row r="7" ht="12.75" customHeight="1" s="91">
       <c r="A7" t="inlineStr">
         <is>
           <t>Benner, Florian</t>
@@ -39660,7 +39678,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="12.75" customHeight="1" s="103">
+    <row r="8" ht="12.75" customHeight="1" s="91">
       <c r="A8" t="inlineStr">
         <is>
           <t>Binnig Andre</t>
@@ -39688,7 +39706,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="14.25" customHeight="1" s="91">
       <c r="A9" t="inlineStr">
         <is>
           <t>Bosch M.</t>
@@ -39714,7 +39732,7 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="14.25" customHeight="1" s="91">
       <c r="A10" t="inlineStr">
         <is>
           <t>Broghammer Marcel</t>
@@ -39765,7 +39783,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="1" s="4">
+    <row r="12" ht="14.25" customFormat="1" customHeight="1" s="4">
       <c r="A12" t="inlineStr">
         <is>
           <t>Ebert M.</t>
@@ -39816,7 +39834,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="14.25" customHeight="1" s="91">
       <c r="A14" t="inlineStr">
         <is>
           <t>Flaig Tim</t>
@@ -39839,7 +39857,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="14.25" customHeight="1" s="91">
       <c r="A15" t="inlineStr">
         <is>
           <t>Fleig Maximilian</t>
@@ -39862,7 +39880,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="1" s="4">
+    <row r="16" ht="14.25" customFormat="1" customHeight="1" s="4">
       <c r="A16" t="inlineStr">
         <is>
           <t>Günter Ralf</t>
@@ -39890,7 +39908,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="1" s="4">
+    <row r="17" ht="14.25" customFormat="1" customHeight="1" s="4">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Haberstroh Raphael</t>
@@ -39918,7 +39936,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="14.25" customHeight="1" s="91">
       <c r="A18" s="92" t="inlineStr">
         <is>
           <t>Hauser Marcel</t>
@@ -39946,7 +39964,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="14.25" customHeight="1" s="91">
       <c r="A19" s="92" t="inlineStr">
         <is>
           <t>Hornberger Christian</t>
@@ -40014,7 +40032,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="14.25" customHeight="1" s="91">
       <c r="A22" s="92" t="inlineStr">
         <is>
           <t>Katzer Florian</t>
@@ -40061,7 +40079,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="14.25" customHeight="1" s="91">
       <c r="A24" s="92" t="inlineStr">
         <is>
           <t>Kuner Andreas</t>
@@ -40105,7 +40123,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="1" s="4">
+    <row r="26" ht="14.25" customFormat="1" customHeight="1" s="4">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Klein Daniel</t>
@@ -40133,7 +40151,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="14.25" customHeight="1" s="91">
       <c r="A27" t="inlineStr">
         <is>
           <t>Klukas Paskal</t>
@@ -40222,7 +40240,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="14.25" customHeight="1" s="91">
       <c r="A31" t="inlineStr">
         <is>
           <t>Löffler Marius</t>
@@ -40250,7 +40268,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="1" s="4">
+    <row r="32" ht="14.25" customFormat="1" customHeight="1" s="4">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Marte Marvin</t>
@@ -40334,7 +40352,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="1" s="4">
+    <row r="35" ht="14.25" customFormat="1" customHeight="1" s="4">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Müller Thorsten</t>
@@ -40362,7 +40380,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="14.25" customHeight="1" s="91">
       <c r="A36" t="inlineStr">
         <is>
           <t>Müller Moritz</t>
@@ -40385,7 +40403,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="14.25" customHeight="1" s="91">
       <c r="A37" t="inlineStr">
         <is>
           <t>Neumaier Tizian</t>
@@ -40406,7 +40424,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="14.25" customHeight="1" s="91">
       <c r="A38" t="inlineStr">
         <is>
           <t>Palmer Lukas</t>
@@ -40477,7 +40495,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="1" s="4">
+    <row r="41" ht="14.25" customFormat="1" customHeight="1" s="4">
       <c r="A41" t="inlineStr">
         <is>
           <t>Preuss, Jonas</t>
@@ -40548,7 +40566,7 @@
         <v/>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="14.25" customHeight="1" s="91">
       <c r="A44" s="92" t="inlineStr">
         <is>
           <t>Schaumann Daniel</t>
@@ -40571,7 +40589,7 @@
         <v/>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="14.25" customHeight="1" s="91">
       <c r="A45" s="92" t="inlineStr">
         <is>
           <t>Schaumann David</t>
@@ -40599,7 +40617,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="1" s="4">
+    <row r="46" ht="14.25" customFormat="1" customHeight="1" s="4">
       <c r="A46" t="inlineStr">
         <is>
           <t>Schaumann Seb</t>
@@ -40627,7 +40645,7 @@
         <v/>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="14.25" customHeight="1" s="91">
       <c r="A47" t="inlineStr">
         <is>
           <t>Scheck Lucas</t>
@@ -40669,7 +40687,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="1" s="4">
+    <row r="49" ht="14.25" customFormat="1" customHeight="1" s="4">
       <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Staiger Tobias</t>
@@ -40721,7 +40739,7 @@
         <v/>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="14.25" customHeight="1" s="91">
       <c r="A51" t="inlineStr">
         <is>
           <t>Thies Yannick</t>
@@ -40742,7 +40760,7 @@
         <v/>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="14.25" customHeight="1" s="91">
       <c r="A52" t="inlineStr">
         <is>
           <t>Tramnitz Christoph</t>
@@ -40796,7 +40814,7 @@
         <v/>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="14.25" customHeight="1" s="91">
       <c r="A54" t="inlineStr">
         <is>
           <t>Verino Roberto</t>
@@ -40879,7 +40897,7 @@
   </mergeCells>
   <printOptions gridLines="1"/>
   <pageMargins left="0.48" right="0.19" top="0.43" bottom="0.48" header="0.34" footer="0.25"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="94"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="89"/>
 </worksheet>
 </file>
 
@@ -40890,26 +40908,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.44140625" customWidth="1" style="103" min="1" max="1"/>
-    <col width="4.109375" customWidth="1" style="103" min="2" max="2"/>
-    <col width="5.44140625" customWidth="1" style="103" min="3" max="3"/>
-    <col width="10.6640625" customWidth="1" style="103" min="4" max="6"/>
-    <col width="35.44140625" customWidth="1" style="103" min="7" max="7"/>
-    <col width="5.88671875" bestFit="1" customWidth="1" style="103" min="8" max="8"/>
-    <col width="5.88671875" customWidth="1" style="103" min="9" max="9"/>
-    <col width="5.44140625" bestFit="1" customWidth="1" style="103" min="10" max="10"/>
+    <col width="18.42578125" customWidth="1" style="91" min="1" max="1"/>
+    <col width="4.140625" customWidth="1" style="91" min="2" max="2"/>
+    <col width="5.42578125" customWidth="1" style="91" min="3" max="3"/>
+    <col width="10.7109375" customWidth="1" style="91" min="4" max="6"/>
+    <col width="35.42578125" customWidth="1" style="91" min="7" max="7"/>
+    <col width="5.85546875" bestFit="1" customWidth="1" style="91" min="8" max="8"/>
+    <col width="5.85546875" customWidth="1" style="91" min="9" max="9"/>
+    <col width="5.42578125" bestFit="1" customWidth="1" style="91" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.75" customHeight="1" s="103">
+    <row r="1" ht="36.75" customHeight="1" s="91">
       <c r="E1" s="99" t="inlineStr">
         <is>
           <t>Saison 22/23</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="79.5" customHeight="1" s="103">
+    <row r="2" ht="79.5" customHeight="1" s="91">
       <c r="A2" s="8" t="n"/>
       <c r="B2" s="8" t="n"/>
       <c r="C2" s="9" t="n"/>
@@ -40934,7 +40952,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.75" customHeight="1" s="103">
+    <row r="3" ht="12.75" customHeight="1" s="91">
       <c r="A3" s="92" t="inlineStr">
         <is>
           <t>Auber, Manuel</t>
@@ -40958,7 +40976,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="12.75" customHeight="1" s="103">
+    <row r="4" ht="12.75" customHeight="1" s="91">
       <c r="A4" s="92" t="inlineStr">
         <is>
           <t>Auber, Daniel</t>
@@ -40982,7 +41000,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="12.75" customHeight="1" s="103">
+    <row r="5" ht="12.75" customHeight="1" s="91">
       <c r="A5" s="92" t="inlineStr">
         <is>
           <t>Auber, David</t>
@@ -41006,7 +41024,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="12.75" customHeight="1" s="103">
+    <row r="6" ht="12.75" customHeight="1" s="91">
       <c r="A6" s="92" t="inlineStr">
         <is>
           <t>Bea, Marc</t>
@@ -41030,7 +41048,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="12.75" customHeight="1" s="103">
+    <row r="7" ht="12.75" customHeight="1" s="91">
       <c r="A7" t="inlineStr">
         <is>
           <t>Benner, Florian</t>
@@ -41059,7 +41077,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="12.75" customHeight="1" s="103">
+    <row r="8" ht="12.75" customHeight="1" s="91">
       <c r="A8" t="inlineStr">
         <is>
           <t>Binnig Andre</t>
@@ -42448,7 +42466,7 @@
   </mergeCells>
   <printOptions gridLines="1"/>
   <pageMargins left="0.48" right="0.19" top="0.43" bottom="0.48" header="0.34" footer="0.25"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="88"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="87"/>
 </worksheet>
 </file>
 
@@ -42459,19 +42477,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.44140625" customWidth="1" style="103" min="1" max="1"/>
-    <col width="4.109375" customWidth="1" style="103" min="2" max="2"/>
-    <col width="5.44140625" customWidth="1" style="103" min="3" max="3"/>
-    <col width="10.6640625" customWidth="1" style="103" min="4" max="6"/>
-    <col width="36.5546875" customWidth="1" style="103" min="7" max="7"/>
-    <col width="5.88671875" bestFit="1" customWidth="1" style="103" min="8" max="8"/>
-    <col width="5.88671875" customWidth="1" style="103" min="9" max="9"/>
-    <col width="5.44140625" bestFit="1" customWidth="1" style="103" min="10" max="10"/>
+    <col width="18.42578125" customWidth="1" style="91" min="1" max="1"/>
+    <col width="4.140625" customWidth="1" style="91" min="2" max="2"/>
+    <col width="5.42578125" customWidth="1" style="91" min="3" max="3"/>
+    <col width="10.7109375" customWidth="1" style="91" min="4" max="6"/>
+    <col width="36.5703125" customWidth="1" style="91" min="7" max="7"/>
+    <col width="5.85546875" bestFit="1" customWidth="1" style="91" min="8" max="8"/>
+    <col width="5.85546875" customWidth="1" style="91" min="9" max="9"/>
+    <col width="5.42578125" bestFit="1" customWidth="1" style="91" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.75" customHeight="1" s="103">
+    <row r="1" ht="36.75" customHeight="1" s="91">
       <c r="A1" t="inlineStr">
         <is>
           <t>Stand: 03.06.2024</t>
@@ -42483,7 +42501,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="79.5" customHeight="1" s="103">
+    <row r="2" ht="79.5" customHeight="1" s="91">
       <c r="A2" s="8" t="n"/>
       <c r="B2" s="8" t="n"/>
       <c r="C2" s="9" t="n"/>
@@ -42508,7 +42526,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.75" customHeight="1" s="103">
+    <row r="3" ht="12.75" customHeight="1" s="91">
       <c r="A3" s="92" t="inlineStr">
         <is>
           <t>Auber, Manuel</t>
@@ -42532,7 +42550,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="12.75" customHeight="1" s="103">
+    <row r="4" ht="12.75" customHeight="1" s="91">
       <c r="A4" s="92" t="inlineStr">
         <is>
           <t>Auber, Daniel</t>
@@ -42556,7 +42574,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="12.75" customHeight="1" s="103">
+    <row r="5" ht="12.75" customHeight="1" s="91">
       <c r="A5" s="92" t="inlineStr">
         <is>
           <t>Auber, David</t>
@@ -42580,7 +42598,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="12.75" customHeight="1" s="103">
+    <row r="6" ht="12.75" customHeight="1" s="91">
       <c r="A6" s="92" t="inlineStr">
         <is>
           <t>Bea, Marc</t>
@@ -44095,17 +44113,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1"/>
+  <dimension ref="A1:R65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col width="20.33203125" customWidth="1" style="103" min="1" max="1"/>
-    <col width="15.44140625" customWidth="1" style="103" min="2" max="2"/>
-    <col width="13.5546875" customWidth="1" style="103" min="3" max="4"/>
-    <col width="13.33203125" customWidth="1" style="103" min="5" max="6"/>
-    <col width="12.5546875" customWidth="1" style="103" min="7" max="8"/>
+    <col width="20.28515625" customWidth="1" style="91" min="1" max="1"/>
+    <col width="15.42578125" customWidth="1" style="91" min="2" max="2"/>
+    <col width="13.5703125" customWidth="1" style="91" min="3" max="4"/>
+    <col width="13.28515625" customWidth="1" style="91" min="5" max="6"/>
+    <col width="12.5703125" customWidth="1" style="91" min="7" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.4" customHeight="1" s="103">
+    <row r="1" ht="23.45" customHeight="1" s="91">
       <c r="A1" s="36" t="n"/>
       <c r="B1" s="88" t="inlineStr">
         <is>
@@ -44129,7 +44147,7 @@
       <c r="Q1" s="38" t="n"/>
       <c r="R1" s="38" t="n"/>
     </row>
-    <row r="2" ht="23.4" customHeight="1" s="103">
+    <row r="2" ht="23.45" customHeight="1" s="91">
       <c r="A2" s="36" t="n"/>
       <c r="B2" s="34" t="n"/>
       <c r="C2" s="34" t="n"/>
@@ -44149,7 +44167,7 @@
       <c r="Q2" s="38" t="n"/>
       <c r="R2" s="38" t="n"/>
     </row>
-    <row r="3" ht="23.4" customHeight="1" s="103">
+    <row r="3" ht="23.45" customHeight="1" s="91">
       <c r="A3" s="35" t="n"/>
       <c r="B3" s="86" t="inlineStr">
         <is>
@@ -44195,7 +44213,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1" s="103">
+    <row r="4" ht="22.5" customHeight="1" s="91">
       <c r="A4" s="35" t="n"/>
       <c r="B4" s="86" t="inlineStr">
         <is>
@@ -44214,43 +44232,43 @@
         </is>
       </c>
       <c r="J4" s="38">
-        <f>COUNTIF($I$8:$I$57,"150")</f>
+        <f>COUNTIF($I$8:$I$58,"150")</f>
         <v/>
       </c>
       <c r="K4" s="38">
-        <f>COUNTIF($I$8:$I$57,"200")</f>
+        <f>COUNTIF($I$8:$I$58,"200")</f>
         <v/>
       </c>
       <c r="L4" s="38">
-        <f>COUNTIF($I$8:$I$57,"250")</f>
+        <f>COUNTIF($I$8:$I$58,"250")</f>
         <v/>
       </c>
       <c r="M4" s="38">
-        <f>COUNTIF($I$8:$I$57,"300")</f>
+        <f>COUNTIF($I$8:$I$58,"300")</f>
         <v/>
       </c>
       <c r="N4" s="38">
-        <f>COUNTIF($I$8:$I$57,"350")</f>
+        <f>COUNTIF($I$8:$I$58,"350")</f>
         <v/>
       </c>
       <c r="O4" s="38">
-        <f>COUNTIF($I$8:$I$57,"400")</f>
+        <f>COUNTIF($I$8:$I$58,"400")</f>
         <v/>
       </c>
       <c r="P4" s="38">
-        <f>COUNTIF($I$8:$I$57,"450")</f>
+        <f>COUNTIF($I$8:$I$58,"450")</f>
         <v/>
       </c>
       <c r="Q4" s="38">
-        <f>COUNTIF($I$8:$I$57,"500")</f>
+        <f>COUNTIF($I$8:$I$58,"500")</f>
         <v/>
       </c>
       <c r="R4" s="38">
-        <f>COUNTIF($I$8:$I$57,"550")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1" s="103">
+        <f>COUNTIF($I$8:$I$58,"550")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1" s="91">
       <c r="A5" s="35" t="n"/>
       <c r="B5" s="86" t="n"/>
       <c r="C5" s="86" t="n"/>
@@ -44270,7 +44288,7 @@
       <c r="Q5" s="38" t="n"/>
       <c r="R5" s="38" t="n"/>
     </row>
-    <row r="6" ht="23.4" customHeight="1" s="103">
+    <row r="6" ht="23.45" customHeight="1" s="91">
       <c r="A6" s="36" t="n"/>
       <c r="B6" s="89" t="inlineStr">
         <is>
@@ -44300,7 +44318,7 @@
       <c r="Q6" s="38" t="n"/>
       <c r="R6" s="38" t="n"/>
     </row>
-    <row r="7" ht="13.95" customHeight="1" s="103">
+    <row r="7" ht="13.9" customHeight="1" s="91">
       <c r="A7" s="35" t="n"/>
       <c r="B7" s="87" t="n"/>
       <c r="C7" s="31" t="inlineStr">
@@ -44344,7 +44362,7 @@
       <c r="Q7" s="38" t="n"/>
       <c r="R7" s="38" t="n"/>
     </row>
-    <row r="8" ht="13.2" customHeight="1" s="103">
+    <row r="8" ht="13.15" customHeight="1" s="91">
       <c r="A8" s="92" t="inlineStr">
         <is>
           <t>Auber, Daniel</t>
@@ -44375,7 +44393,7 @@
       </c>
       <c r="I8" s="32" t="n"/>
     </row>
-    <row r="9" ht="13.2" customHeight="1" s="103">
+    <row r="9" ht="13.15" customHeight="1" s="91">
       <c r="A9" s="92" t="inlineStr">
         <is>
           <t>Auber, David</t>
@@ -44406,7 +44424,7 @@
       </c>
       <c r="I9" s="32" t="n"/>
     </row>
-    <row r="10" ht="13.2" customHeight="1" s="103">
+    <row r="10" ht="13.15" customHeight="1" s="91">
       <c r="A10" s="92" t="inlineStr">
         <is>
           <t>Auber, Manuel</t>
@@ -44437,10 +44455,10 @@
       </c>
       <c r="I10" s="32" t="n"/>
     </row>
-    <row r="11" ht="13.2" customHeight="1" s="103">
+    <row r="11" ht="13.15" customHeight="1" s="91">
       <c r="A11" s="92" t="inlineStr">
         <is>
-          <t>Auber, Matthias**</t>
+          <t>Auber, Matthias</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -44468,7 +44486,7 @@
       </c>
       <c r="I11" s="32" t="n"/>
     </row>
-    <row r="12" ht="13.2" customHeight="1" s="103">
+    <row r="12" ht="13.15" customHeight="1" s="91">
       <c r="A12" s="92" t="inlineStr">
         <is>
           <t>Bamboi, Daniel</t>
@@ -44493,7 +44511,7 @@
       </c>
       <c r="I12" s="32" t="n"/>
     </row>
-    <row r="13" ht="13.2" customHeight="1" s="103">
+    <row r="13" ht="13.15" customHeight="1" s="91">
       <c r="A13" s="92" t="inlineStr">
         <is>
           <t>Bea, Marc</t>
@@ -44524,7 +44542,7 @@
       </c>
       <c r="I13" s="32" t="n"/>
     </row>
-    <row r="14" ht="13.2" customHeight="1" s="103">
+    <row r="14" ht="13.15" customHeight="1" s="91">
       <c r="A14" s="92" t="inlineStr">
         <is>
           <t>Benner, Florian</t>
@@ -44555,7 +44573,7 @@
       </c>
       <c r="I14" s="32" t="n"/>
     </row>
-    <row r="15" ht="13.2" customHeight="1" s="103">
+    <row r="15" ht="13.15" customHeight="1" s="91">
       <c r="A15" s="92" t="inlineStr">
         <is>
           <t>Binnig, Andre</t>
@@ -44586,7 +44604,7 @@
       </c>
       <c r="I15" s="32" t="n"/>
     </row>
-    <row r="16" ht="13.2" customHeight="1" s="103">
+    <row r="16" ht="13.15" customHeight="1" s="91">
       <c r="A16" s="92" t="inlineStr">
         <is>
           <t>Broghammer, Marcel</t>
@@ -44617,10 +44635,10 @@
       </c>
       <c r="I16" s="32" t="n"/>
     </row>
-    <row r="17" ht="13.2" customHeight="1" s="103">
+    <row r="17" ht="13.15" customHeight="1" s="91">
       <c r="A17" s="92" t="inlineStr">
         <is>
-          <t>Bühner, Ahmad</t>
+          <t>Bühner, Ahmad Reza</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -44648,10 +44666,10 @@
       </c>
       <c r="I17" s="32" t="n"/>
     </row>
-    <row r="18" ht="13.2" customHeight="1" s="103">
+    <row r="18" ht="13.15" customHeight="1" s="91">
       <c r="A18" s="92" t="inlineStr">
         <is>
-          <t>Coraci, Davide*</t>
+          <t>Coraci, Davide</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -44679,7 +44697,7 @@
       </c>
       <c r="I18" s="32" t="n"/>
     </row>
-    <row r="19" ht="13.2" customHeight="1" s="103">
+    <row r="19" ht="13.15" customHeight="1" s="91">
       <c r="A19" s="92" t="inlineStr">
         <is>
           <t>Dold, Markus</t>
@@ -44712,7 +44730,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" ht="13.2" customHeight="1" s="103">
+    <row r="20" ht="13.15" customHeight="1" s="91">
       <c r="A20" s="92" t="inlineStr">
         <is>
           <t>Ebert, Matthias</t>
@@ -44743,7 +44761,7 @@
       </c>
       <c r="I20" s="33" t="n"/>
     </row>
-    <row r="21" ht="13.2" customHeight="1" s="103">
+    <row r="21" ht="13.15" customHeight="1" s="91">
       <c r="A21" s="92" t="inlineStr">
         <is>
           <t>Flaig, Elias</t>
@@ -44774,7 +44792,7 @@
       </c>
       <c r="I21" s="33" t="n"/>
     </row>
-    <row r="22" ht="13.2" customHeight="1" s="103">
+    <row r="22" ht="13.15" customHeight="1" s="91">
       <c r="A22" s="92" t="inlineStr">
         <is>
           <t>Flaig, Luis</t>
@@ -44805,26 +44823,27 @@
       </c>
       <c r="I22" s="33" t="n"/>
     </row>
-    <row r="23" ht="13.2" customHeight="1" s="103">
+    <row r="23" ht="13.15" customHeight="1" s="91">
       <c r="A23" s="92" t="inlineStr">
         <is>
-          <t>Flaig, Tim</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>111</v>
+          <t>Katzer, Florian</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>'23-24'!G23</f>
+        <v/>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <f>SUM(C23:F23)</f>
@@ -44836,23 +44855,23 @@
       </c>
       <c r="I23" s="33" t="n"/>
     </row>
-    <row r="24" ht="13.2" customHeight="1" s="103">
+    <row r="24" ht="13.15" customHeight="1" s="91">
       <c r="A24" s="92" t="inlineStr">
         <is>
-          <t>Fleig, Maximilian</t>
+          <t>Flaig, Tim</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -44867,20 +44886,20 @@
       </c>
       <c r="I24" s="33" t="n"/>
     </row>
-    <row r="25" ht="13.2" customHeight="1" s="103">
+    <row r="25" ht="13.15" customHeight="1" s="91">
       <c r="A25" s="92" t="inlineStr">
         <is>
-          <t>Günter, Ralf</t>
+          <t>Fleig, Maximilian</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>332</v>
+        <v>162</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>5</v>
@@ -44896,30 +44915,28 @@
         <f>B25+G25</f>
         <v/>
       </c>
-      <c r="I25" s="33" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="26" ht="13.2" customHeight="1" s="103">
+      <c r="I25" s="33" t="n"/>
+    </row>
+    <row r="26" ht="13.15" customHeight="1" s="91">
       <c r="A26" s="92" t="inlineStr">
         <is>
-          <t>Haberstroh, Raphael</t>
+          <t>Günter, Ralf</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C26" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26">
         <f>SUM(C26:F26)</f>
@@ -44933,17 +44950,17 @@
         <v>350</v>
       </c>
     </row>
-    <row r="27" ht="13.2" customHeight="1" s="103">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Hoch, Philipp**</t>
+    <row r="27" ht="13.15" customHeight="1" s="91">
+      <c r="A27" s="92" t="inlineStr">
+        <is>
+          <t>Haberstroh, Raphael</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -44962,27 +44979,30 @@
         <f>B27+G27</f>
         <v/>
       </c>
-    </row>
-    <row r="28" ht="13.2" customHeight="1" s="103">
-      <c r="A28" s="92" t="inlineStr">
-        <is>
-          <t>Hornberger, Christian</t>
+      <c r="I27" s="33" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="28" ht="13.15" customHeight="1" s="91">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hoch, Philipp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <f>SUM(C28:F28)</f>
@@ -44992,30 +45012,27 @@
         <f>B28+G28</f>
         <v/>
       </c>
-      <c r="I28" s="33" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="29" ht="13.2" customHeight="1" s="103">
+    </row>
+    <row r="29" ht="13.15" customHeight="1" s="91">
       <c r="A29" s="92" t="inlineStr">
         <is>
-          <t>Kimmich, Simeon</t>
+          <t>Hornberger, Christian</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29">
         <f>SUM(C29:F29)</f>
@@ -45026,29 +45043,29 @@
         <v/>
       </c>
       <c r="I29" s="33" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" ht="13.2" customHeight="1" s="103">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" ht="13.15" customHeight="1" s="91">
       <c r="A30" s="92" t="inlineStr">
         <is>
-          <t>Klein, Daniel</t>
+          <t>Kimmich, Simeon</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>413</v>
+        <v>146</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <f>SUM(C30:F30)</f>
@@ -45058,28 +45075,30 @@
         <f>B30+G30</f>
         <v/>
       </c>
-      <c r="I30" s="33" t="n"/>
-    </row>
-    <row r="31" ht="13.2" customHeight="1" s="103">
+      <c r="I30" s="33" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" ht="13.15" customHeight="1" s="91">
       <c r="A31" s="92" t="inlineStr">
         <is>
-          <t>Klukas, Pascal</t>
+          <t>Klein, Daniel</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>79</v>
+        <v>413</v>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <f>SUM(C31:F31)</f>
@@ -45091,26 +45110,26 @@
       </c>
       <c r="I31" s="33" t="n"/>
     </row>
-    <row r="32" ht="13.2" customHeight="1" s="103">
+    <row r="32" ht="13.15" customHeight="1" s="91">
       <c r="A32" s="92" t="inlineStr">
         <is>
-          <t>Kobel, Michael</t>
+          <t>Klukas, Pascal</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
         <f>SUM(C32:F32)</f>
@@ -45122,23 +45141,23 @@
       </c>
       <c r="I32" s="33" t="n"/>
     </row>
-    <row r="33" ht="13.2" customHeight="1" s="103">
+    <row r="33" ht="13.15" customHeight="1" s="91">
       <c r="A33" s="92" t="inlineStr">
         <is>
-          <t>Kuner, Andreas</t>
+          <t>Kobel, Michael</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="C33" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -45151,30 +45170,28 @@
         <f>B33+G33</f>
         <v/>
       </c>
-      <c r="I33" s="33" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" ht="13.2" customHeight="1" s="103">
+      <c r="I33" s="33" t="n"/>
+    </row>
+    <row r="34" ht="13.15" customHeight="1" s="91">
       <c r="A34" s="92" t="inlineStr">
         <is>
-          <t>Kunz, Holger</t>
+          <t>Kuner, Andreas</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="C34" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <f>SUM(C34:F34)</f>
@@ -45184,28 +45201,30 @@
         <f>B34+G34</f>
         <v/>
       </c>
-      <c r="I34" s="33" t="n"/>
-    </row>
-    <row r="35" ht="13.2" customHeight="1" s="103">
+      <c r="I34" s="33" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" ht="13.15" customHeight="1" s="91">
       <c r="A35" s="92" t="inlineStr">
         <is>
-          <t>Leingruber, Fabian**</t>
+          <t>Kunz, Holger</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <f>SUM(C35:F35)</f>
@@ -45217,26 +45236,26 @@
       </c>
       <c r="I35" s="33" t="n"/>
     </row>
-    <row r="36" ht="13.2" customHeight="1" s="103">
+    <row r="36" ht="13.15" customHeight="1" s="91">
       <c r="A36" s="92" t="inlineStr">
         <is>
-          <t>Linder, Andreas</t>
+          <t>Leingruber, Fabian</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <f>SUM(C36:F36)</f>
@@ -45248,26 +45267,26 @@
       </c>
       <c r="I36" s="33" t="n"/>
     </row>
-    <row r="37" ht="13.2" customHeight="1" s="103">
+    <row r="37" ht="13.15" customHeight="1" s="91">
       <c r="A37" s="92" t="inlineStr">
         <is>
-          <t>Lobert, Marius</t>
+          <t>Linder, Andreas</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C37" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <f>SUM(C37:F37)</f>
@@ -45277,27 +45296,25 @@
         <f>B37+G37</f>
         <v/>
       </c>
-      <c r="I37" s="33" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" ht="13.2" customHeight="1" s="103">
+      <c r="I37" s="33" t="n"/>
+    </row>
+    <row r="38" ht="13.15" customHeight="1" s="91">
       <c r="A38" s="92" t="inlineStr">
         <is>
-          <t>Löffler, Marius</t>
+          <t>Lobert, Marius</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>341</v>
+        <v>143</v>
       </c>
       <c r="C38" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -45311,26 +45328,26 @@
         <v/>
       </c>
       <c r="I38" s="33" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="39" ht="13.2" customHeight="1" s="103">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" ht="13.15" customHeight="1" s="91">
       <c r="A39" s="92" t="inlineStr">
         <is>
-          <t>Müller, Andre</t>
+          <t>Löffler, Marius</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>124</v>
+        <v>341</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -45343,25 +45360,27 @@
         <f>B39+G39</f>
         <v/>
       </c>
-      <c r="I39" s="33" t="n"/>
-    </row>
-    <row r="40" ht="13.2" customHeight="1" s="103">
+      <c r="I39" s="33" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="40" ht="13.15" customHeight="1" s="91">
       <c r="A40" s="92" t="inlineStr">
         <is>
-          <t>Müller, Felix</t>
+          <t>Müller, Andre</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>216</v>
+        <v>124</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -45376,23 +45395,23 @@
       </c>
       <c r="I40" s="33" t="n"/>
     </row>
-    <row r="41" ht="13.2" customHeight="1" s="103">
+    <row r="41" ht="13.15" customHeight="1" s="91">
       <c r="A41" s="92" t="inlineStr">
         <is>
-          <t>Müller, Moritz</t>
+          <t>Müller, Felix</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>121</v>
+        <v>216</v>
       </c>
       <c r="C41" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -45407,23 +45426,23 @@
       </c>
       <c r="I41" s="33" t="n"/>
     </row>
-    <row r="42" ht="13.2" customHeight="1" s="103">
+    <row r="42" ht="13.15" customHeight="1" s="91">
       <c r="A42" s="92" t="inlineStr">
         <is>
-          <t>Müller, Thorsten</t>
+          <t>Müller, Moritz</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>236</v>
+        <v>121</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -45438,23 +45457,23 @@
       </c>
       <c r="I42" s="33" t="n"/>
     </row>
-    <row r="43" ht="13.2" customHeight="1" s="103">
+    <row r="43" ht="13.15" customHeight="1" s="91">
       <c r="A43" s="92" t="inlineStr">
         <is>
-          <t>Palmer, Micha</t>
+          <t>Müller, Thorsten</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>44</v>
+        <v>236</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -45469,23 +45488,23 @@
       </c>
       <c r="I43" s="33" t="n"/>
     </row>
-    <row r="44" ht="13.2" customHeight="1" s="103">
+    <row r="44" ht="13.15" customHeight="1" s="91">
       <c r="A44" s="92" t="inlineStr">
         <is>
-          <t>Pfundstein, Andreas</t>
+          <t>Palmer, Micha</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -45500,26 +45519,26 @@
       </c>
       <c r="I44" s="33" t="n"/>
     </row>
-    <row r="45" ht="13.2" customHeight="1" s="103">
+    <row r="45" ht="13.15" customHeight="1" s="91">
       <c r="A45" s="92" t="inlineStr">
         <is>
-          <t>Preuss, Jonas</t>
+          <t>Pfundstein, Andreas</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>399</v>
+        <v>133</v>
       </c>
       <c r="C45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45">
         <f>SUM(C45:F45)</f>
@@ -45529,30 +45548,28 @@
         <f>B45+G45</f>
         <v/>
       </c>
-      <c r="I45" s="33" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="46" ht="13.2" customHeight="1" s="103">
+      <c r="I45" s="33" t="n"/>
+    </row>
+    <row r="46" ht="13.15" customHeight="1" s="91">
       <c r="A46" s="92" t="inlineStr">
         <is>
-          <t>Reuter, Johannes</t>
+          <t>Preuss, Jonas</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>281</v>
+        <v>399</v>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46">
         <f>SUM(C46:F46)</f>
@@ -45562,25 +45579,27 @@
         <f>B46+G46</f>
         <v/>
       </c>
-      <c r="I46" s="33" t="n"/>
-    </row>
-    <row r="47" ht="13.2" customHeight="1" s="103">
+      <c r="I46" s="33" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47" ht="13.15" customHeight="1" s="91">
       <c r="A47" s="92" t="inlineStr">
         <is>
-          <t>Schaumann, Daniel</t>
+          <t>Reuter, Johannes</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>161</v>
+        <v>281</v>
       </c>
       <c r="C47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>2</v>
@@ -45595,23 +45614,23 @@
       </c>
       <c r="I47" s="33" t="n"/>
     </row>
-    <row r="48" ht="13.2" customHeight="1" s="103">
+    <row r="48" ht="13.15" customHeight="1" s="91">
       <c r="A48" s="92" t="inlineStr">
         <is>
-          <t>Schaumann, David</t>
+          <t>Schaumann, Daniel</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="C48" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
@@ -45624,30 +45643,28 @@
         <f>B48+G48</f>
         <v/>
       </c>
-      <c r="I48" s="33" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="49" ht="13.2" customHeight="1" s="103">
+      <c r="I48" s="33" t="n"/>
+    </row>
+    <row r="49" ht="13.15" customHeight="1" s="91">
       <c r="A49" s="92" t="inlineStr">
         <is>
-          <t>Schaumann, Sebastian</t>
+          <t>Schaumann, David</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49">
         <f>SUM(C49:F49)</f>
@@ -45657,28 +45674,30 @@
         <f>B49+G49</f>
         <v/>
       </c>
-      <c r="I49" s="32" t="n"/>
-    </row>
-    <row r="50" ht="13.2" customHeight="1" s="103">
+      <c r="I49" s="33" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" ht="13.15" customHeight="1" s="91">
       <c r="A50" s="92" t="inlineStr">
         <is>
-          <t>Scheck, Lucas</t>
+          <t>Schaumann, Sebastian</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50">
         <f>SUM(C50:F50)</f>
@@ -45690,17 +45709,17 @@
       </c>
       <c r="I50" s="32" t="n"/>
     </row>
-    <row r="51" ht="13.2" customHeight="1" s="103">
+    <row r="51" ht="13.15" customHeight="1" s="91">
       <c r="A51" s="92" t="inlineStr">
         <is>
-          <t>Schwenk, Kevin*</t>
+          <t>Scheck, Lucas</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -45721,17 +45740,17 @@
       </c>
       <c r="I51" s="32" t="n"/>
     </row>
-    <row r="52" ht="13.2" customHeight="1" s="103">
+    <row r="52" ht="13.15" customHeight="1" s="91">
       <c r="A52" s="92" t="inlineStr">
         <is>
-          <t>Seidel, Jan</t>
+          <t>Schwenk, Kevin</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -45752,23 +45771,23 @@
       </c>
       <c r="I52" s="32" t="n"/>
     </row>
-    <row r="53" ht="13.2" customHeight="1" s="103">
+    <row r="53" ht="13.15" customHeight="1" s="91">
       <c r="A53" s="92" t="inlineStr">
         <is>
-          <t>Staiger, Tobias</t>
+          <t>Seidel, Jan</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>500</v>
+        <v>49</v>
       </c>
       <c r="C53" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -45783,23 +45802,23 @@
       </c>
       <c r="I53" s="32" t="n"/>
     </row>
-    <row r="54" ht="13.2" customHeight="1" s="103">
+    <row r="54" ht="13.15" customHeight="1" s="91">
       <c r="A54" s="92" t="inlineStr">
         <is>
-          <t>Tramnitz, Christoph</t>
+          <t>Staiger, Tobias</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>263</v>
+        <v>500</v>
       </c>
       <c r="C54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -45814,23 +45833,23 @@
       </c>
       <c r="I54" s="32" t="n"/>
     </row>
-    <row r="55" ht="13.2" customHeight="1" s="103">
+    <row r="55" ht="13.15" customHeight="1" s="91">
       <c r="A55" s="92" t="inlineStr">
         <is>
-          <t>Tramnitz, Lukas</t>
+          <t>Tramnitz, Christoph</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -45845,23 +45864,23 @@
       </c>
       <c r="I55" s="32" t="n"/>
     </row>
-    <row r="56" ht="13.2" customHeight="1" s="103">
+    <row r="56" ht="13.15" customHeight="1" s="91">
       <c r="A56" s="92" t="inlineStr">
         <is>
-          <t>Verrino, Roberto</t>
+          <t>Tramnitz, Lukas</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>301</v>
+        <v>157</v>
       </c>
       <c r="C56" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -45876,26 +45895,26 @@
       </c>
       <c r="I56" s="32" t="n"/>
     </row>
-    <row r="57" ht="13.2" customHeight="1" s="103">
+    <row r="57" ht="13.15" customHeight="1" s="91">
       <c r="A57" s="92" t="inlineStr">
         <is>
-          <t>Weber, Peter</t>
+          <t>Verrino, Roberto</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="C57" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57">
         <f>SUM(C57:F57)</f>
@@ -45907,17 +45926,48 @@
       </c>
       <c r="I57" s="32" t="n"/>
     </row>
-    <row r="58" ht="13.2" customHeight="1" s="103"/>
-    <row r="59" ht="13.2" customHeight="1" s="103"/>
-    <row r="60" ht="13.2" customHeight="1" s="103"/>
-    <row r="61" ht="13.2" customHeight="1" s="103"/>
-    <row r="62" ht="13.2" customHeight="1" s="103">
-      <c r="B62" s="102" t="n"/>
-      <c r="F62" s="72" t="n"/>
-    </row>
-    <row r="63" ht="13.2" customHeight="1" s="103"/>
-    <row r="64" ht="12.75" customHeight="1" s="103">
-      <c r="B64" s="73" t="n"/>
+    <row r="58" ht="13.15" customHeight="1" s="91">
+      <c r="A58" s="92" t="inlineStr">
+        <is>
+          <t>Weber, Peter</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>26</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58">
+        <f>SUM(C58:F58)</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>B58+G58</f>
+        <v/>
+      </c>
+      <c r="I58" s="32" t="n"/>
+    </row>
+    <row r="59" ht="13.15" customHeight="1" s="91"/>
+    <row r="60" ht="13.15" customHeight="1" s="91"/>
+    <row r="61" ht="13.15" customHeight="1" s="91"/>
+    <row r="62" ht="13.15" customHeight="1" s="91"/>
+    <row r="63" ht="13.15" customHeight="1" s="91">
+      <c r="B63" s="74" t="n"/>
+      <c r="F63" s="72" t="n"/>
+    </row>
+    <row r="64" ht="13.15" customHeight="1" s="91"/>
+    <row r="65" ht="12.75" customHeight="1" s="91">
+      <c r="B65" s="73" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -45927,7 +45977,7 @@
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="B6:B7"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:R58">
+  <conditionalFormatting sqref="A8:R59">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/player_stats/_stats_overall.xlsx
+++ b/player_stats/_stats_overall.xlsx
@@ -328,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -550,22 +550,16 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -573,12 +567,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -6942,8 +6930,8 @@
         <f>G8+B8</f>
         <v/>
       </c>
-      <c r="I8" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B8&lt;$J$3:$R$3)*(H8&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I8" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B8&lt;$J$3:$R$3)*(H8&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J8" s="101" t="n"/>
@@ -6984,8 +6972,8 @@
         <f>G9+B9</f>
         <v/>
       </c>
-      <c r="I9" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B9&lt;$J$3:$R$3)*(H9&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I9" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B9&lt;$J$3:$R$3)*(H9&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J9" s="104" t="n"/>
@@ -7026,8 +7014,8 @@
         <f>G10+B10</f>
         <v/>
       </c>
-      <c r="I10" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B10&lt;$J$3:$R$3)*(H10&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I10" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B10&lt;$J$3:$R$3)*(H10&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J10" s="101" t="n"/>
@@ -7068,8 +7056,8 @@
         <f>G11+B11</f>
         <v/>
       </c>
-      <c r="I11" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B11&lt;$J$3:$R$3)*(H11&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I11" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B11&lt;$J$3:$R$3)*(H11&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J11" s="104" t="n"/>
@@ -7110,8 +7098,8 @@
         <f>G12+B12</f>
         <v/>
       </c>
-      <c r="I12" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B12&lt;$J$3:$R$3)*(H12&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I12" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B12&lt;$J$3:$R$3)*(H12&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J12" s="101" t="n"/>
@@ -7152,8 +7140,8 @@
         <f>G13+B13</f>
         <v/>
       </c>
-      <c r="I13" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B13&lt;$J$3:$R$3)*(H13&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I13" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B13&lt;$J$3:$R$3)*(H13&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J13" s="104" t="n"/>
@@ -7194,8 +7182,8 @@
         <f>G14+B14</f>
         <v/>
       </c>
-      <c r="I14" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B14&lt;$J$3:$R$3)*(H14&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I14" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B14&lt;$J$3:$R$3)*(H14&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J14" s="101" t="n"/>
@@ -7236,8 +7224,8 @@
         <f>G15+B15</f>
         <v/>
       </c>
-      <c r="I15" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B15&lt;$J$3:$R$3)*(H15&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I15" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B15&lt;$J$3:$R$3)*(H15&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J15" s="104" t="n"/>
@@ -7278,8 +7266,8 @@
         <f>G16+B16</f>
         <v/>
       </c>
-      <c r="I16" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B16&lt;$J$3:$R$3)*(H16&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I16" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B16&lt;$J$3:$R$3)*(H16&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J16" s="101" t="n"/>
@@ -7320,8 +7308,8 @@
         <f>G17+B17</f>
         <v/>
       </c>
-      <c r="I17" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B17&lt;$J$3:$R$3)*(H17&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I17" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B17&lt;$J$3:$R$3)*(H17&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J17" s="104" t="n"/>
@@ -7362,8 +7350,8 @@
         <f>G18+B18</f>
         <v/>
       </c>
-      <c r="I18" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B18&lt;$J$3:$R$3)*(H18&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I18" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B18&lt;$J$3:$R$3)*(H18&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J18" s="101" t="n"/>
@@ -7404,8 +7392,8 @@
         <f>G19+B19</f>
         <v/>
       </c>
-      <c r="I19" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B19&lt;$J$3:$R$3)*(H19&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I19" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B19&lt;$J$3:$R$3)*(H19&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J19" s="104" t="n"/>
@@ -7446,8 +7434,8 @@
         <f>G20+B20</f>
         <v/>
       </c>
-      <c r="I20" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B20&lt;$J$3:$R$3)*(H20&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I20" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B20&lt;$J$3:$R$3)*(H20&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J20" s="101" t="n"/>
@@ -7488,8 +7476,8 @@
         <f>G21+B21</f>
         <v/>
       </c>
-      <c r="I21" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B21&lt;$J$3:$R$3)*(H21&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I21" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B21&lt;$J$3:$R$3)*(H21&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J21" s="104" t="n"/>
@@ -7530,8 +7518,8 @@
         <f>G22+B22</f>
         <v/>
       </c>
-      <c r="I22" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B22&lt;$J$3:$R$3)*(H22&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I22" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B22&lt;$J$3:$R$3)*(H22&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J22" s="101" t="n"/>
@@ -7572,8 +7560,8 @@
         <f>G23+B23</f>
         <v/>
       </c>
-      <c r="I23" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B23&lt;$J$3:$R$3)*(H23&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I23" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B23&lt;$J$3:$R$3)*(H23&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J23" s="104" t="n"/>
@@ -7614,8 +7602,8 @@
         <f>G24+B24</f>
         <v/>
       </c>
-      <c r="I24" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B24&lt;$J$3:$R$3)*(H24&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I24" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B24&lt;$J$3:$R$3)*(H24&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J24" s="101" t="n"/>
@@ -7656,8 +7644,8 @@
         <f>G25+B25</f>
         <v/>
       </c>
-      <c r="I25" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B25&lt;$J$3:$R$3)*(H25&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I25" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B25&lt;$J$3:$R$3)*(H25&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J25" s="104" t="n"/>
@@ -7698,8 +7686,8 @@
         <f>G26+B26</f>
         <v/>
       </c>
-      <c r="I26" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B26&lt;$J$3:$R$3)*(H26&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I26" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B26&lt;$J$3:$R$3)*(H26&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J26" s="101" t="n"/>
@@ -7740,8 +7728,8 @@
         <f>G27+B27</f>
         <v/>
       </c>
-      <c r="I27" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B27&lt;$J$3:$R$3)*(H27&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I27" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B27&lt;$J$3:$R$3)*(H27&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J27" s="104" t="n"/>
@@ -7783,7 +7771,7 @@
         <v/>
       </c>
       <c r="I28" s="106">
-        <f>IFERROR(LOOKUP(2,1/((B28&lt;$J$3:$R$3)*(H28&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <f>IFERROR(LOOKUP(2,1/((B28&lt;$J$3:$R$3)*(H28&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J28" s="101" t="n"/>
@@ -7824,8 +7812,8 @@
         <f>G29+B29</f>
         <v/>
       </c>
-      <c r="I29" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B29&lt;$J$3:$R$3)*(H29&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I29" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B29&lt;$J$3:$R$3)*(H29&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J29" s="104" t="n"/>
@@ -7866,8 +7854,8 @@
         <f>G30+B30</f>
         <v/>
       </c>
-      <c r="I30" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B30&lt;$J$3:$R$3)*(H30&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I30" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B30&lt;$J$3:$R$3)*(H30&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J30" s="101" t="n"/>
@@ -7908,8 +7896,8 @@
         <f>G31+B31</f>
         <v/>
       </c>
-      <c r="I31" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B31&lt;$J$3:$R$3)*(H31&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I31" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B31&lt;$J$3:$R$3)*(H31&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J31" s="104" t="n"/>
@@ -7950,8 +7938,8 @@
         <f>G32+B32</f>
         <v/>
       </c>
-      <c r="I32" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B32&lt;$J$3:$R$3)*(H32&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I32" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B32&lt;$J$3:$R$3)*(H32&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J32" s="101" t="n"/>
@@ -7992,8 +7980,8 @@
         <f>G33+B33</f>
         <v/>
       </c>
-      <c r="I33" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B33&lt;$J$3:$R$3)*(H33&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I33" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B33&lt;$J$3:$R$3)*(H33&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J33" s="104" t="n"/>
@@ -8034,8 +8022,8 @@
         <f>G34+B34</f>
         <v/>
       </c>
-      <c r="I34" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B34&lt;$J$3:$R$3)*(H34&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I34" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B34&lt;$J$3:$R$3)*(H34&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J34" s="101" t="n"/>
@@ -8076,8 +8064,8 @@
         <f>G35+B35</f>
         <v/>
       </c>
-      <c r="I35" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B35&lt;$J$3:$R$3)*(H35&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I35" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B35&lt;$J$3:$R$3)*(H35&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J35" s="104" t="n"/>
@@ -8118,8 +8106,8 @@
         <f>G36+B36</f>
         <v/>
       </c>
-      <c r="I36" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B36&lt;$J$3:$R$3)*(H36&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I36" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B36&lt;$J$3:$R$3)*(H36&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J36" s="101" t="n"/>
@@ -8160,8 +8148,8 @@
         <f>G37+B37</f>
         <v/>
       </c>
-      <c r="I37" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B37&lt;$J$3:$R$3)*(H37&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I37" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B37&lt;$J$3:$R$3)*(H37&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J37" s="104" t="n"/>
@@ -8202,8 +8190,8 @@
         <f>G38+B38</f>
         <v/>
       </c>
-      <c r="I38" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B38&lt;$J$3:$R$3)*(H38&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I38" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B38&lt;$J$3:$R$3)*(H38&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J38" s="101" t="n"/>
@@ -8244,8 +8232,8 @@
         <f>G39+B39</f>
         <v/>
       </c>
-      <c r="I39" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B39&lt;$J$3:$R$3)*(H39&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I39" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B39&lt;$J$3:$R$3)*(H39&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J39" s="104" t="n"/>
@@ -8286,8 +8274,8 @@
         <f>G40+B40</f>
         <v/>
       </c>
-      <c r="I40" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B40&lt;$J$3:$R$3)*(H40&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I40" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B40&lt;$J$3:$R$3)*(H40&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J40" s="101" t="n"/>
@@ -8328,8 +8316,8 @@
         <f>G41+B41</f>
         <v/>
       </c>
-      <c r="I41" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B41&lt;$J$3:$R$3)*(H41&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I41" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B41&lt;$J$3:$R$3)*(H41&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J41" s="104" t="n"/>
@@ -8370,8 +8358,8 @@
         <f>G42+B42</f>
         <v/>
       </c>
-      <c r="I42" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B42&lt;$J$3:$R$3)*(H42&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I42" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B42&lt;$J$3:$R$3)*(H42&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J42" s="101" t="n"/>
@@ -8412,8 +8400,8 @@
         <f>G43+B43</f>
         <v/>
       </c>
-      <c r="I43" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B43&lt;$J$3:$R$3)*(H43&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I43" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B43&lt;$J$3:$R$3)*(H43&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J43" s="104" t="n"/>
@@ -8454,8 +8442,8 @@
         <f>G44+B44</f>
         <v/>
       </c>
-      <c r="I44" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B44&lt;$J$3:$R$3)*(H44&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I44" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B44&lt;$J$3:$R$3)*(H44&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J44" s="101" t="n"/>
@@ -8496,8 +8484,8 @@
         <f>G45+B45</f>
         <v/>
       </c>
-      <c r="I45" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B45&lt;$J$3:$R$3)*(H45&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I45" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B45&lt;$J$3:$R$3)*(H45&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J45" s="104" t="n"/>
@@ -8538,8 +8526,8 @@
         <f>G46+B46</f>
         <v/>
       </c>
-      <c r="I46" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B46&lt;$J$3:$R$3)*(H46&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I46" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B46&lt;$J$3:$R$3)*(H46&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J46" s="101" t="n"/>
@@ -8580,8 +8568,8 @@
         <f>G47+B47</f>
         <v/>
       </c>
-      <c r="I47" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B47&lt;$J$3:$R$3)*(H47&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I47" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B47&lt;$J$3:$R$3)*(H47&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J47" s="104" t="n"/>
@@ -8622,8 +8610,8 @@
         <f>G48+B48</f>
         <v/>
       </c>
-      <c r="I48" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B48&lt;$J$3:$R$3)*(H48&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I48" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B48&lt;$J$3:$R$3)*(H48&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J48" s="101" t="n"/>
@@ -8664,8 +8652,8 @@
         <f>G49+B49</f>
         <v/>
       </c>
-      <c r="I49" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B49&lt;$J$3:$R$3)*(H49&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I49" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B49&lt;$J$3:$R$3)*(H49&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J49" s="104" t="n"/>
@@ -8706,8 +8694,8 @@
         <f>G50+B50</f>
         <v/>
       </c>
-      <c r="I50" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B50&lt;$J$3:$R$3)*(H50&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I50" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B50&lt;$J$3:$R$3)*(H50&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J50" s="101" t="n"/>
@@ -8748,8 +8736,8 @@
         <f>G51+B51</f>
         <v/>
       </c>
-      <c r="I51" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B51&lt;$J$3:$R$3)*(H51&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I51" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B51&lt;$J$3:$R$3)*(H51&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J51" s="104" t="n"/>
@@ -8790,8 +8778,8 @@
         <f>G52+B52</f>
         <v/>
       </c>
-      <c r="I52" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B52&lt;$J$3:$R$3)*(H52&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I52" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B52&lt;$J$3:$R$3)*(H52&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J52" s="101" t="n"/>
@@ -8832,8 +8820,8 @@
         <f>G53+B53</f>
         <v/>
       </c>
-      <c r="I53" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B53&lt;$J$3:$R$3)*(H53&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I53" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B53&lt;$J$3:$R$3)*(H53&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J53" s="104" t="n"/>
@@ -8874,8 +8862,8 @@
         <f>G54+B54</f>
         <v/>
       </c>
-      <c r="I54" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B54&lt;$J$3:$R$3)*(H54&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I54" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B54&lt;$J$3:$R$3)*(H54&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J54" s="101" t="n"/>
@@ -8916,8 +8904,8 @@
         <f>G55+B55</f>
         <v/>
       </c>
-      <c r="I55" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B55&lt;$J$3:$R$3)*(H55&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I55" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B55&lt;$J$3:$R$3)*(H55&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J55" s="104" t="n"/>
@@ -8958,8 +8946,8 @@
         <f>G56+B56</f>
         <v/>
       </c>
-      <c r="I56" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B56&lt;$J$3:$R$3)*(H56&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I56" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B56&lt;$J$3:$R$3)*(H56&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J56" s="101" t="n"/>
@@ -9000,8 +8988,8 @@
         <f>G57+B57</f>
         <v/>
       </c>
-      <c r="I57" s="114">
-        <f>IFERROR(LOOKUP(2,1/((B57&lt;$J$3:$R$3)*(H57&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I57" s="105">
+        <f>IFERROR(LOOKUP(2,1/((B57&lt;$J$3:$R$3)*(H57&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J57" s="104" t="n"/>
@@ -9042,8 +9030,8 @@
         <f>G58+B58</f>
         <v/>
       </c>
-      <c r="I58" s="113">
-        <f>IFERROR(LOOKUP(2,1/((B58&lt;$J$3:$R$3)*(H58&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+      <c r="I58" s="102">
+        <f>IFERROR(LOOKUP(2,1/((B58&lt;$J$3:$R$3)*(H58&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J58" s="101" t="n"/>
@@ -9085,7 +9073,7 @@
         <v/>
       </c>
       <c r="I59" s="107">
-        <f>IFERROR(LOOKUP(2,1/((B59&lt;$J$3:$R$3)*(H59&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <f>IFERROR(LOOKUP(2,1/((B59&lt;$J$3:$R$3)*(H59&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J59" s="104" t="n"/>
@@ -9127,7 +9115,7 @@
         <v/>
       </c>
       <c r="I60" s="106">
-        <f>IFERROR(LOOKUP(2,1/((B60&lt;$J$3:$R$3)*(H60&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <f>IFERROR(LOOKUP(2,1/((B60&lt;$J$3:$R$3)*(H60&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J60" s="101" t="n"/>
@@ -9169,7 +9157,7 @@
         <v/>
       </c>
       <c r="I61" s="107">
-        <f>IFERROR(LOOKUP(2,1/((B61&lt;$J$3:$R$3)*(H61&gt;$J$3:$R$3)),$J$3:$R$3),"")</f>
+        <f>IFERROR(LOOKUP(2,1/((B61&lt;$J$3:$R$3)*(H61&gt;=$J$3:$R$3)),$J$3:$R$3),"")</f>
         <v/>
       </c>
       <c r="J61" s="104" t="n"/>
@@ -9204,11 +9192,11 @@
     </row>
     <row r="63" ht="13.15" customHeight="1" s="91">
       <c r="A63" s="104" t="n"/>
-      <c r="B63" s="110" t="n"/>
+      <c r="B63" s="108" t="n"/>
       <c r="C63" s="104" t="n"/>
       <c r="D63" s="104" t="n"/>
       <c r="E63" s="104" t="n"/>
-      <c r="F63" s="111" t="n"/>
+      <c r="F63" s="109" t="n"/>
       <c r="G63" s="104" t="n"/>
       <c r="H63" s="104" t="n"/>
       <c r="I63" s="107" t="n"/>
@@ -9244,7 +9232,7 @@
     </row>
     <row r="65" ht="12.75" customHeight="1" s="91">
       <c r="A65" s="104" t="n"/>
-      <c r="B65" s="112" t="n"/>
+      <c r="B65" s="110" t="n"/>
       <c r="C65" s="104" t="n"/>
       <c r="D65" s="104" t="n"/>
       <c r="E65" s="104" t="n"/>

--- a/player_stats/_stats_overall.xlsx
+++ b/player_stats/_stats_overall.xlsx
@@ -6757,7 +6757,7 @@
       <c r="A4" s="35" t="n"/>
       <c r="B4" s="86" t="inlineStr">
         <is>
-          <t>Stand 12.05.2026</t>
+          <t>Stand 27.05.2026</t>
         </is>
       </c>
       <c r="C4" s="87" t="n"/>
